--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_entertainment.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_entertainment.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09656479240007401</v>
+        <v>0.09635713041907382</v>
       </c>
       <c r="C2">
-        <v>420.0859975882316</v>
+        <v>416.6607996285488</v>
       </c>
       <c r="D2">
-        <v>353.0859975882316</v>
+        <v>353.9197996285488</v>
       </c>
       <c r="E2">
-        <v>-53</v>
+        <v>-48.741</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.258999999999999</v>
       </c>
       <c r="G2">
         <v>67</v>
@@ -1439,28 +1439,28 @@
         <v>40.3</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2142277</v>
       </c>
       <c r="N2">
-        <v>40.3</v>
+        <v>40.0857723</v>
       </c>
       <c r="O2">
-        <v>10.075</v>
+        <v>10.021443075</v>
       </c>
       <c r="P2">
-        <v>30.225</v>
+        <v>30.06432922499999</v>
       </c>
       <c r="Q2">
-        <v>31.425</v>
+        <v>31.26432922499999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09656479240007401</v>
+        <v>0.09694937416068063</v>
       </c>
       <c r="T2">
-        <v>1.017512237681883</v>
+        <v>1.025220663724927</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>188.1175963705907</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09635713041907382</v>
+        <v>0.09614946843807365</v>
       </c>
       <c r="C3">
-        <v>416.6607996285488</v>
+        <v>413.2395489875838</v>
       </c>
       <c r="D3">
-        <v>353.9197996285488</v>
+        <v>354.7575489875837</v>
       </c>
       <c r="E3">
-        <v>-48.741</v>
+        <v>-44.482</v>
       </c>
       <c r="F3">
-        <v>4.258999999999999</v>
+        <v>8.517999999999999</v>
       </c>
       <c r="G3">
         <v>67</v>
@@ -1521,28 +1521,28 @@
         <v>40.3</v>
       </c>
       <c r="M3">
-        <v>0.2142277</v>
+        <v>0.4284553999999999</v>
       </c>
       <c r="N3">
-        <v>40.0857723</v>
+        <v>39.8715446</v>
       </c>
       <c r="O3">
-        <v>10.021443075</v>
+        <v>9.96788615</v>
       </c>
       <c r="P3">
-        <v>30.06432922499999</v>
+        <v>29.90365845</v>
       </c>
       <c r="Q3">
-        <v>31.26432922499999</v>
+        <v>31.10365845</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09694937416068063</v>
+        <v>0.09734180452864657</v>
       </c>
       <c r="T3">
-        <v>1.025220663724927</v>
+        <v>1.033086404585177</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>188.1175963705907</v>
+        <v>94.05879818529539</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09614946843807365</v>
+        <v>0.09594180645707345</v>
       </c>
       <c r="C4">
-        <v>413.2395489875838</v>
+        <v>409.8222737624635</v>
       </c>
       <c r="D4">
-        <v>354.7575489875837</v>
+        <v>355.5992737624635</v>
       </c>
       <c r="E4">
-        <v>-44.482</v>
+        <v>-40.223</v>
       </c>
       <c r="F4">
-        <v>8.517999999999999</v>
+        <v>12.777</v>
       </c>
       <c r="G4">
         <v>67</v>
@@ -1603,28 +1603,28 @@
         <v>40.3</v>
       </c>
       <c r="M4">
-        <v>0.4284553999999999</v>
+        <v>0.6426831</v>
       </c>
       <c r="N4">
-        <v>39.8715446</v>
+        <v>39.6573169</v>
       </c>
       <c r="O4">
-        <v>9.96788615</v>
+        <v>9.914329224999999</v>
       </c>
       <c r="P4">
-        <v>29.90365845</v>
+        <v>29.742987675</v>
       </c>
       <c r="Q4">
-        <v>31.10365845</v>
+        <v>30.942987675</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09734180452864657</v>
+        <v>0.09774232624440563</v>
       </c>
       <c r="T4">
-        <v>1.033086404585177</v>
+        <v>1.041114325669349</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>94.05879818529539</v>
+        <v>62.70586545686358</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09594180645707345</v>
+        <v>0.09573414447607327</v>
       </c>
       <c r="C5">
-        <v>409.8222737624635</v>
+        <v>406.4090023176105</v>
       </c>
       <c r="D5">
-        <v>355.5992737624635</v>
+        <v>356.4450023176105</v>
       </c>
       <c r="E5">
-        <v>-40.223</v>
+        <v>-35.964</v>
       </c>
       <c r="F5">
-        <v>12.777</v>
+        <v>17.036</v>
       </c>
       <c r="G5">
         <v>67</v>
@@ -1685,28 +1685,28 @@
         <v>40.3</v>
       </c>
       <c r="M5">
-        <v>0.6426831</v>
+        <v>0.8569107999999999</v>
       </c>
       <c r="N5">
-        <v>39.6573169</v>
+        <v>39.4430892</v>
       </c>
       <c r="O5">
-        <v>9.914329224999999</v>
+        <v>9.860772299999999</v>
       </c>
       <c r="P5">
-        <v>29.742987675</v>
+        <v>29.5823169</v>
       </c>
       <c r="Q5">
-        <v>30.942987675</v>
+        <v>30.78231689999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09774232624440563</v>
+        <v>0.09815119216257633</v>
       </c>
       <c r="T5">
-        <v>1.041114325669349</v>
+        <v>1.049309495109441</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>62.70586545686358</v>
+        <v>47.02939909264769</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09573414447607327</v>
+        <v>0.09552648249507309</v>
       </c>
       <c r="C6">
-        <v>406.4090023176105</v>
+        <v>402.9997632879295</v>
       </c>
       <c r="D6">
-        <v>356.4450023176105</v>
+        <v>357.2947632879295</v>
       </c>
       <c r="E6">
-        <v>-35.964</v>
+        <v>-31.705</v>
       </c>
       <c r="F6">
-        <v>17.036</v>
+        <v>21.295</v>
       </c>
       <c r="G6">
         <v>67</v>
@@ -1767,28 +1767,28 @@
         <v>40.3</v>
       </c>
       <c r="M6">
-        <v>0.8569107999999999</v>
+        <v>1.0711385</v>
       </c>
       <c r="N6">
-        <v>39.4430892</v>
+        <v>39.22886149999999</v>
       </c>
       <c r="O6">
-        <v>9.860772299999999</v>
+        <v>9.807215374999998</v>
       </c>
       <c r="P6">
-        <v>29.5823169</v>
+        <v>29.421646125</v>
       </c>
       <c r="Q6">
-        <v>30.78231689999999</v>
+        <v>30.62164612499999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09815119216257633</v>
+        <v>0.09856866578428745</v>
       </c>
       <c r="T6">
-        <v>1.049309495109441</v>
+        <v>1.057677194432483</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>47.02939909264769</v>
+        <v>37.62351927411814</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09552648249507309</v>
+        <v>0.09531882051407289</v>
       </c>
       <c r="C7">
-        <v>402.9997632879295</v>
+        <v>399.5945855820387</v>
       </c>
       <c r="D7">
-        <v>357.2947632879295</v>
+        <v>358.1485855820387</v>
       </c>
       <c r="E7">
-        <v>-31.705</v>
+        <v>-27.446</v>
       </c>
       <c r="F7">
-        <v>21.295</v>
+        <v>25.554</v>
       </c>
       <c r="G7">
         <v>67</v>
@@ -1849,28 +1849,28 @@
         <v>40.3</v>
       </c>
       <c r="M7">
-        <v>1.0711385</v>
+        <v>1.2853662</v>
       </c>
       <c r="N7">
-        <v>39.22886149999999</v>
+        <v>39.0146338</v>
       </c>
       <c r="O7">
-        <v>9.807215374999998</v>
+        <v>9.75365845</v>
       </c>
       <c r="P7">
-        <v>29.421646125</v>
+        <v>29.26097535</v>
       </c>
       <c r="Q7">
-        <v>30.62164612499999</v>
+        <v>30.46097535</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09856866578428745</v>
+        <v>0.0989950218234818</v>
       </c>
       <c r="T7">
-        <v>1.057677194432483</v>
+        <v>1.066222929911334</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>37.62351927411814</v>
+        <v>31.35293272843179</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09531882051407289</v>
+        <v>0.09511115853307271</v>
       </c>
       <c r="C8">
-        <v>399.5945855820387</v>
+        <v>396.1934983855483</v>
       </c>
       <c r="D8">
-        <v>358.1485855820387</v>
+        <v>359.0064983855483</v>
       </c>
       <c r="E8">
-        <v>-27.446</v>
+        <v>-23.187</v>
       </c>
       <c r="F8">
-        <v>25.554</v>
+        <v>29.813</v>
       </c>
       <c r="G8">
         <v>67</v>
@@ -1931,28 +1931,28 @@
         <v>40.3</v>
       </c>
       <c r="M8">
-        <v>1.2853662</v>
+        <v>1.4995939</v>
       </c>
       <c r="N8">
-        <v>39.0146338</v>
+        <v>38.8004061</v>
       </c>
       <c r="O8">
-        <v>9.75365845</v>
+        <v>9.700101524999999</v>
       </c>
       <c r="P8">
-        <v>29.26097535</v>
+        <v>29.100304575</v>
       </c>
       <c r="Q8">
-        <v>30.46097535</v>
+        <v>30.30030457499999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0989950218234818</v>
+        <v>0.0994305468097556</v>
       </c>
       <c r="T8">
-        <v>1.066222929911334</v>
+        <v>1.074952444647795</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>31.35293272843179</v>
+        <v>26.87394233865582</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0951111585330727</v>
+        <v>0.09490349655207253</v>
       </c>
       <c r="C9">
-        <v>396.1934983855484</v>
+        <v>392.7965311643861</v>
       </c>
       <c r="D9">
-        <v>359.0064983855484</v>
+        <v>359.8685311643861</v>
       </c>
       <c r="E9">
-        <v>-23.187</v>
+        <v>-18.928</v>
       </c>
       <c r="F9">
-        <v>29.813</v>
+        <v>34.072</v>
       </c>
       <c r="G9">
         <v>67</v>
@@ -2013,28 +2013,28 @@
         <v>40.3</v>
       </c>
       <c r="M9">
-        <v>1.4995939</v>
+        <v>1.7138216</v>
       </c>
       <c r="N9">
-        <v>38.8004061</v>
+        <v>38.58617839999999</v>
       </c>
       <c r="O9">
-        <v>9.700101524999999</v>
+        <v>9.646544599999999</v>
       </c>
       <c r="P9">
-        <v>29.100304575</v>
+        <v>28.9396338</v>
       </c>
       <c r="Q9">
-        <v>30.30030457499999</v>
+        <v>30.1396338</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0994305468097556</v>
+        <v>0.09987553973051362</v>
       </c>
       <c r="T9">
-        <v>1.074952444647795</v>
+        <v>1.083871731443744</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>26.87394233865582</v>
+        <v>23.51469954632384</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09490349655207253</v>
+        <v>0.09469583457107235</v>
       </c>
       <c r="C10">
-        <v>392.7965311643861</v>
+        <v>389.4037136681709</v>
       </c>
       <c r="D10">
-        <v>359.8685311643861</v>
+        <v>360.7347136681709</v>
       </c>
       <c r="E10">
-        <v>-18.928</v>
+        <v>-14.669</v>
       </c>
       <c r="F10">
-        <v>34.072</v>
+        <v>38.331</v>
       </c>
       <c r="G10">
         <v>67</v>
@@ -2095,28 +2095,28 @@
         <v>40.3</v>
       </c>
       <c r="M10">
-        <v>1.7138216</v>
+        <v>1.9280493</v>
       </c>
       <c r="N10">
-        <v>38.58617839999999</v>
+        <v>38.3719507</v>
       </c>
       <c r="O10">
-        <v>9.646544599999999</v>
+        <v>9.592987675</v>
       </c>
       <c r="P10">
-        <v>28.9396338</v>
+        <v>28.778963025</v>
       </c>
       <c r="Q10">
-        <v>30.1396338</v>
+        <v>29.978963025</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09987553973051362</v>
+        <v>0.1003303127154641</v>
       </c>
       <c r="T10">
-        <v>1.083871731443744</v>
+        <v>1.092987046520923</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.51469954632384</v>
+        <v>20.90195515228786</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09469583457107235</v>
+        <v>0.09448817259007215</v>
       </c>
       <c r="C11">
-        <v>389.4037136681709</v>
+        <v>386.0150759336352</v>
       </c>
       <c r="D11">
-        <v>360.7347136681709</v>
+        <v>361.6050759336352</v>
       </c>
       <c r="E11">
-        <v>-14.669</v>
+        <v>-10.41</v>
       </c>
       <c r="F11">
-        <v>38.331</v>
+        <v>42.59</v>
       </c>
       <c r="G11">
         <v>67</v>
@@ -2177,28 +2177,28 @@
         <v>40.3</v>
       </c>
       <c r="M11">
-        <v>1.9280493</v>
+        <v>2.142277</v>
       </c>
       <c r="N11">
-        <v>38.3719507</v>
+        <v>38.157723</v>
       </c>
       <c r="O11">
-        <v>9.592987675</v>
+        <v>9.539430749999999</v>
       </c>
       <c r="P11">
-        <v>28.778963025</v>
+        <v>28.61829225</v>
       </c>
       <c r="Q11">
-        <v>29.978963025</v>
+        <v>29.81829225</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1003303127154641</v>
+        <v>0.1007951917667468</v>
       </c>
       <c r="T11">
-        <v>1.092987046520923</v>
+        <v>1.102304924155373</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>20.90195515228786</v>
+        <v>18.81175963705908</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09448817259007215</v>
+        <v>0.09428051060907197</v>
       </c>
       <c r="C12">
-        <v>386.0150759336352</v>
+        <v>382.6306482880964</v>
       </c>
       <c r="D12">
-        <v>361.6050759336352</v>
+        <v>362.4796482880964</v>
       </c>
       <c r="E12">
-        <v>-10.41</v>
+        <v>-6.151000000000003</v>
       </c>
       <c r="F12">
-        <v>42.59</v>
+        <v>46.849</v>
       </c>
       <c r="G12">
         <v>67</v>
@@ -2259,28 +2259,28 @@
         <v>40.3</v>
       </c>
       <c r="M12">
-        <v>2.142277</v>
+        <v>2.3565047</v>
       </c>
       <c r="N12">
-        <v>38.157723</v>
+        <v>37.9434953</v>
       </c>
       <c r="O12">
-        <v>9.539430749999999</v>
+        <v>9.485873824999999</v>
       </c>
       <c r="P12">
-        <v>28.61829225</v>
+        <v>28.457621475</v>
       </c>
       <c r="Q12">
-        <v>29.81829225</v>
+        <v>29.657621475</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1007951917667468</v>
+        <v>0.1012705175382831</v>
       </c>
       <c r="T12">
-        <v>1.102304924155373</v>
+        <v>1.111832192298462</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.81175963705907</v>
+        <v>17.1015996700537</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09428051060907197</v>
+        <v>0.09407284862807179</v>
       </c>
       <c r="C13">
-        <v>382.6306482880964</v>
+        <v>379.2504613529807</v>
       </c>
       <c r="D13">
-        <v>362.4796482880964</v>
+        <v>363.3584613529807</v>
       </c>
       <c r="E13">
-        <v>-6.151000000000003</v>
+        <v>-1.892000000000003</v>
       </c>
       <c r="F13">
-        <v>46.849</v>
+        <v>51.108</v>
       </c>
       <c r="G13">
         <v>67</v>
@@ -2341,28 +2341,28 @@
         <v>40.3</v>
       </c>
       <c r="M13">
-        <v>2.3565047</v>
+        <v>2.5707324</v>
       </c>
       <c r="N13">
-        <v>37.9434953</v>
+        <v>37.7292676</v>
       </c>
       <c r="O13">
-        <v>9.485873824999999</v>
+        <v>9.4323169</v>
       </c>
       <c r="P13">
-        <v>28.457621475</v>
+        <v>28.2969507</v>
       </c>
       <c r="Q13">
-        <v>29.657621475</v>
+        <v>29.4969507</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1012705175382831</v>
+        <v>0.1017566461682634</v>
       </c>
       <c r="T13">
-        <v>1.111832192298462</v>
+        <v>1.121575989262984</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.1015996700537</v>
+        <v>15.6764663642159</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09407284862807179</v>
+        <v>0.09386518664707159</v>
       </c>
       <c r="C14">
-        <v>379.2504613529807</v>
+        <v>375.8745460473954</v>
       </c>
       <c r="D14">
-        <v>363.3584613529807</v>
+        <v>364.2415460473954</v>
       </c>
       <c r="E14">
-        <v>-1.892000000000003</v>
+        <v>2.366999999999997</v>
       </c>
       <c r="F14">
-        <v>51.108</v>
+        <v>55.367</v>
       </c>
       <c r="G14">
         <v>67</v>
@@ -2423,28 +2423,28 @@
         <v>40.3</v>
       </c>
       <c r="M14">
-        <v>2.5707324</v>
+        <v>2.7849601</v>
       </c>
       <c r="N14">
-        <v>37.7292676</v>
+        <v>37.5150399</v>
       </c>
       <c r="O14">
-        <v>9.4323169</v>
+        <v>9.378759974999999</v>
       </c>
       <c r="P14">
-        <v>28.2969507</v>
+        <v>28.136279925</v>
       </c>
       <c r="Q14">
-        <v>29.4969507</v>
+        <v>29.336279925</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1017566461682634</v>
+        <v>0.1022539501690478</v>
       </c>
       <c r="T14">
-        <v>1.121575989262984</v>
+        <v>1.131543781560024</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.6764663642159</v>
+        <v>14.47058433619929</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09386518664707159</v>
+        <v>0.09365752466607141</v>
       </c>
       <c r="C15">
-        <v>375.8745460473954</v>
+        <v>372.5029335917566</v>
       </c>
       <c r="D15">
-        <v>364.2415460473954</v>
+        <v>365.1289335917566</v>
       </c>
       <c r="E15">
-        <v>2.366999999999997</v>
+        <v>6.626000000000005</v>
       </c>
       <c r="F15">
-        <v>55.367</v>
+        <v>59.626</v>
       </c>
       <c r="G15">
         <v>67</v>
@@ -2505,28 +2505,28 @@
         <v>40.3</v>
       </c>
       <c r="M15">
-        <v>2.7849601</v>
+        <v>2.9991878</v>
       </c>
       <c r="N15">
-        <v>37.5150399</v>
+        <v>37.3008122</v>
       </c>
       <c r="O15">
-        <v>9.378759974999999</v>
+        <v>9.325203049999999</v>
       </c>
       <c r="P15">
-        <v>28.136279925</v>
+        <v>27.97560915</v>
       </c>
       <c r="Q15">
-        <v>29.336279925</v>
+        <v>29.17560915</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1022539501690478</v>
+        <v>0.1027628193791528</v>
       </c>
       <c r="T15">
-        <v>1.131543781560024</v>
+        <v>1.141743382980252</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.47058433619929</v>
+        <v>13.43697116932791</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09365752466607141</v>
+        <v>0.09361861268507123</v>
       </c>
       <c r="C16">
-        <v>372.5029335917566</v>
+        <v>368.4106946913397</v>
       </c>
       <c r="D16">
-        <v>365.1289335917566</v>
+        <v>365.2956946913397</v>
       </c>
       <c r="E16">
-        <v>6.626000000000005</v>
+        <v>10.88500000000001</v>
       </c>
       <c r="F16">
-        <v>59.626</v>
+        <v>63.88500000000001</v>
       </c>
       <c r="G16">
         <v>67</v>
@@ -2587,45 +2587,45 @@
         <v>40.3</v>
       </c>
       <c r="M16">
-        <v>2.9991878</v>
+        <v>3.309243</v>
       </c>
       <c r="N16">
-        <v>37.3008122</v>
+        <v>36.990757</v>
       </c>
       <c r="O16">
-        <v>9.325203049999999</v>
+        <v>9.247689249999999</v>
       </c>
       <c r="P16">
-        <v>27.97560915</v>
+        <v>27.74306774999999</v>
       </c>
       <c r="Q16">
-        <v>29.17560915</v>
+        <v>28.94306774999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1027628193791528</v>
+        <v>0.1032836619824367</v>
       </c>
       <c r="T16">
-        <v>1.141743382980252</v>
+        <v>1.152182975022132</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.43697116932791</v>
+        <v>12.1780117084179</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09361861268507123</v>
+        <v>0.09342220070407105</v>
       </c>
       <c r="C17">
-        <v>368.4106946913397</v>
+        <v>364.9957677485453</v>
       </c>
       <c r="D17">
-        <v>365.2956946913397</v>
+        <v>366.1397677485454</v>
       </c>
       <c r="E17">
-        <v>10.88499999999999</v>
+        <v>15.14399999999999</v>
       </c>
       <c r="F17">
-        <v>63.88499999999999</v>
+        <v>68.14399999999999</v>
       </c>
       <c r="G17">
         <v>67</v>
@@ -2669,28 +2669,28 @@
         <v>40.3</v>
       </c>
       <c r="M17">
-        <v>3.309242999999999</v>
+        <v>3.529859199999999</v>
       </c>
       <c r="N17">
-        <v>36.990757</v>
+        <v>36.7701408</v>
       </c>
       <c r="O17">
-        <v>9.247689249999999</v>
+        <v>9.1925352</v>
       </c>
       <c r="P17">
-        <v>27.74306774999999</v>
+        <v>27.5776056</v>
       </c>
       <c r="Q17">
-        <v>28.94306774999999</v>
+        <v>28.7776056</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1032836619824367</v>
+        <v>0.1038169056000846</v>
       </c>
       <c r="T17">
-        <v>1.152182975022132</v>
+        <v>1.162871128779294</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.17801170841791</v>
+        <v>11.41688597664179</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09342220070407105</v>
+        <v>0.09322578872307087</v>
       </c>
       <c r="C18">
-        <v>364.9957677485453</v>
+        <v>361.5847505665181</v>
       </c>
       <c r="D18">
-        <v>366.1397677485454</v>
+        <v>366.9877505665181</v>
       </c>
       <c r="E18">
-        <v>15.14399999999999</v>
+        <v>19.40300000000001</v>
       </c>
       <c r="F18">
-        <v>68.14399999999999</v>
+        <v>72.40300000000001</v>
       </c>
       <c r="G18">
         <v>67</v>
@@ -2751,28 +2751,28 @@
         <v>40.3</v>
       </c>
       <c r="M18">
-        <v>3.529859199999999</v>
+        <v>3.7504754</v>
       </c>
       <c r="N18">
-        <v>36.7701408</v>
+        <v>36.5495246</v>
       </c>
       <c r="O18">
-        <v>9.1925352</v>
+        <v>9.13738115</v>
       </c>
       <c r="P18">
-        <v>27.5776056</v>
+        <v>27.41214345</v>
       </c>
       <c r="Q18">
-        <v>28.7776056</v>
+        <v>28.61214345</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1038169056000846</v>
+        <v>0.1043629984615312</v>
       </c>
       <c r="T18">
-        <v>1.162871128779294</v>
+        <v>1.173816828410124</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.41688597664179</v>
+        <v>10.74530444860403</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09322578872307087</v>
+        <v>0.09302937674207068</v>
       </c>
       <c r="C19">
-        <v>361.5847505665181</v>
+        <v>358.1776703734365</v>
       </c>
       <c r="D19">
-        <v>366.9877505665181</v>
+        <v>367.8396703734365</v>
       </c>
       <c r="E19">
-        <v>19.40300000000001</v>
+        <v>23.66200000000001</v>
       </c>
       <c r="F19">
-        <v>72.40300000000001</v>
+        <v>76.66200000000001</v>
       </c>
       <c r="G19">
         <v>67</v>
@@ -2833,28 +2833,28 @@
         <v>40.3</v>
       </c>
       <c r="M19">
-        <v>3.7504754</v>
+        <v>3.9710916</v>
       </c>
       <c r="N19">
-        <v>36.5495246</v>
+        <v>36.3289084</v>
       </c>
       <c r="O19">
-        <v>9.13738115</v>
+        <v>9.082227099999999</v>
       </c>
       <c r="P19">
-        <v>27.41214345</v>
+        <v>27.2466813</v>
       </c>
       <c r="Q19">
-        <v>28.61214345</v>
+        <v>28.4466813</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1043629984615312</v>
+        <v>0.1049224106610618</v>
       </c>
       <c r="T19">
-        <v>1.173816828410124</v>
+        <v>1.185029496324632</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.74530444860403</v>
+        <v>10.14834309034825</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09302937674207069</v>
+        <v>0.0930752147610705</v>
       </c>
       <c r="C20">
-        <v>358.1776703734364</v>
+        <v>353.7194983398624</v>
       </c>
       <c r="D20">
-        <v>367.8396703734364</v>
+        <v>367.6404983398624</v>
       </c>
       <c r="E20">
-        <v>23.66199999999999</v>
+        <v>27.92099999999999</v>
       </c>
       <c r="F20">
-        <v>76.66199999999999</v>
+        <v>80.92099999999999</v>
       </c>
       <c r="G20">
         <v>67</v>
@@ -2915,45 +2915,45 @@
         <v>40.3</v>
       </c>
       <c r="M20">
-        <v>3.971091599999999</v>
+        <v>4.329273499999999</v>
       </c>
       <c r="N20">
-        <v>36.3289084</v>
+        <v>35.9707265</v>
       </c>
       <c r="O20">
-        <v>9.082227099999999</v>
+        <v>8.992681624999999</v>
       </c>
       <c r="P20">
-        <v>27.2466813</v>
+        <v>26.978044875</v>
       </c>
       <c r="Q20">
-        <v>28.4466813</v>
+        <v>28.178044875</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1049224106610618</v>
+        <v>0.1054956355074944</v>
       </c>
       <c r="T20">
-        <v>1.185029496324632</v>
+        <v>1.196519020237029</v>
       </c>
       <c r="U20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>10.14834309034826</v>
+        <v>9.308721197679011</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0930752147610705</v>
+        <v>0.09289155278007033</v>
       </c>
       <c r="C21">
-        <v>353.7194983398624</v>
+        <v>350.2598351189739</v>
       </c>
       <c r="D21">
-        <v>367.6404983398624</v>
+        <v>368.4398351189739</v>
       </c>
       <c r="E21">
-        <v>27.92099999999999</v>
+        <v>32.18000000000001</v>
       </c>
       <c r="F21">
-        <v>80.92099999999999</v>
+        <v>85.18000000000001</v>
       </c>
       <c r="G21">
         <v>67</v>
@@ -2997,28 +2997,28 @@
         <v>40.3</v>
       </c>
       <c r="M21">
-        <v>4.329273499999999</v>
+        <v>4.55713</v>
       </c>
       <c r="N21">
-        <v>35.9707265</v>
+        <v>35.74287</v>
       </c>
       <c r="O21">
-        <v>8.992681624999999</v>
+        <v>8.935717499999999</v>
       </c>
       <c r="P21">
-        <v>26.978044875</v>
+        <v>26.8071525</v>
       </c>
       <c r="Q21">
-        <v>28.178044875</v>
+        <v>28.0071525</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1054956355074944</v>
+        <v>0.1060831909750879</v>
       </c>
       <c r="T21">
-        <v>1.196519020237029</v>
+        <v>1.208295782247236</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.308721197679011</v>
+        <v>8.843285137795059</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09289155278007033</v>
+        <v>0.09270789079907013</v>
       </c>
       <c r="C22">
-        <v>350.2598351189739</v>
+        <v>346.8036553637016</v>
       </c>
       <c r="D22">
-        <v>368.4398351189739</v>
+        <v>369.2426553637017</v>
       </c>
       <c r="E22">
-        <v>32.18000000000001</v>
+        <v>36.43900000000001</v>
       </c>
       <c r="F22">
-        <v>85.18000000000001</v>
+        <v>89.43900000000001</v>
       </c>
       <c r="G22">
         <v>67</v>
@@ -3079,28 +3079,28 @@
         <v>40.3</v>
       </c>
       <c r="M22">
-        <v>4.55713</v>
+        <v>4.7849865</v>
       </c>
       <c r="N22">
-        <v>35.74287</v>
+        <v>35.51501349999999</v>
       </c>
       <c r="O22">
-        <v>8.935717499999999</v>
+        <v>8.878753374999999</v>
       </c>
       <c r="P22">
-        <v>26.8071525</v>
+        <v>26.636260125</v>
       </c>
       <c r="Q22">
-        <v>28.0071525</v>
+        <v>27.836260125</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1060831909750879</v>
+        <v>0.1066856212646457</v>
       </c>
       <c r="T22">
-        <v>1.208295782247236</v>
+        <v>1.220370690131119</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.843285137795059</v>
+        <v>8.422176321709578</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09270789079907013</v>
+        <v>0.09252422881806995</v>
       </c>
       <c r="C23">
-        <v>346.8036553637016</v>
+        <v>343.3509818948982</v>
       </c>
       <c r="D23">
-        <v>369.2426553637017</v>
+        <v>370.0489818948982</v>
       </c>
       <c r="E23">
-        <v>36.43899999999999</v>
+        <v>40.69799999999999</v>
       </c>
       <c r="F23">
-        <v>89.43899999999999</v>
+        <v>93.69799999999999</v>
       </c>
       <c r="G23">
         <v>67</v>
@@ -3161,28 +3161,28 @@
         <v>40.3</v>
       </c>
       <c r="M23">
-        <v>4.7849865</v>
+        <v>5.012842999999999</v>
       </c>
       <c r="N23">
-        <v>35.51501349999999</v>
+        <v>35.287157</v>
       </c>
       <c r="O23">
-        <v>8.878753374999999</v>
+        <v>8.82178925</v>
       </c>
       <c r="P23">
-        <v>26.636260125</v>
+        <v>26.46536775</v>
       </c>
       <c r="Q23">
-        <v>27.836260125</v>
+        <v>27.66536775</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1066856212646457</v>
+        <v>0.1073034984847051</v>
       </c>
       <c r="T23">
-        <v>1.220370690131119</v>
+        <v>1.232755211037665</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.42217632170958</v>
+        <v>8.039350125268237</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09252422881806995</v>
+        <v>0.09234056683706976</v>
       </c>
       <c r="C24">
-        <v>343.3509818948982</v>
+        <v>339.9018377331909</v>
       </c>
       <c r="D24">
-        <v>370.0489818948982</v>
+        <v>370.8588377331909</v>
       </c>
       <c r="E24">
-        <v>40.69799999999999</v>
+        <v>44.95699999999999</v>
       </c>
       <c r="F24">
-        <v>93.69799999999999</v>
+        <v>97.95699999999999</v>
       </c>
       <c r="G24">
         <v>67</v>
@@ -3243,28 +3243,28 @@
         <v>40.3</v>
       </c>
       <c r="M24">
-        <v>5.012842999999999</v>
+        <v>5.2406995</v>
       </c>
       <c r="N24">
-        <v>35.287157</v>
+        <v>35.0593005</v>
       </c>
       <c r="O24">
-        <v>8.82178925</v>
+        <v>8.764825125</v>
       </c>
       <c r="P24">
-        <v>26.46536775</v>
+        <v>26.294475375</v>
       </c>
       <c r="Q24">
-        <v>27.66536775</v>
+        <v>27.494475375</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1073034984847051</v>
+        <v>0.1079374244637269</v>
       </c>
       <c r="T24">
-        <v>1.232755211037665</v>
+        <v>1.245461407811915</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.039350125268237</v>
+        <v>7.689813163300052</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09234056683706976</v>
+        <v>0.09230090485606957</v>
       </c>
       <c r="C25">
-        <v>339.9018377331909</v>
+        <v>335.8181924996084</v>
       </c>
       <c r="D25">
-        <v>370.8588377331909</v>
+        <v>371.0341924996084</v>
       </c>
       <c r="E25">
-        <v>44.95699999999999</v>
+        <v>49.21600000000001</v>
       </c>
       <c r="F25">
-        <v>97.95699999999999</v>
+        <v>102.216</v>
       </c>
       <c r="G25">
         <v>67</v>
@@ -3325,45 +3325,45 @@
         <v>40.3</v>
       </c>
       <c r="M25">
-        <v>5.2406995</v>
+        <v>5.550328800000001</v>
       </c>
       <c r="N25">
-        <v>35.0593005</v>
+        <v>34.74967119999999</v>
       </c>
       <c r="O25">
-        <v>8.764825125</v>
+        <v>8.687417799999999</v>
       </c>
       <c r="P25">
-        <v>26.294475375</v>
+        <v>26.0622534</v>
       </c>
       <c r="Q25">
-        <v>27.494475375</v>
+        <v>27.2622534</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1079374244637269</v>
+        <v>0.1085880327053547</v>
       </c>
       <c r="T25">
-        <v>1.245461407811915</v>
+        <v>1.258501978185486</v>
       </c>
       <c r="U25">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y25">
-        <v>7.689813163300052</v>
+        <v>7.260831106077894</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09230090485606957</v>
+        <v>0.0921232428750694</v>
       </c>
       <c r="C26">
-        <v>335.8181924996084</v>
+        <v>332.3467164887363</v>
       </c>
       <c r="D26">
-        <v>371.0341924996084</v>
+        <v>371.8217164887363</v>
       </c>
       <c r="E26">
-        <v>49.21599999999999</v>
+        <v>53.47499999999999</v>
       </c>
       <c r="F26">
-        <v>102.216</v>
+        <v>106.475</v>
       </c>
       <c r="G26">
         <v>67</v>
@@ -3407,28 +3407,28 @@
         <v>40.3</v>
       </c>
       <c r="M26">
-        <v>5.5503288</v>
+        <v>5.781592499999999</v>
       </c>
       <c r="N26">
-        <v>34.74967119999999</v>
+        <v>34.5184075</v>
       </c>
       <c r="O26">
-        <v>8.687417799999999</v>
+        <v>8.629601874999999</v>
       </c>
       <c r="P26">
-        <v>26.0622534</v>
+        <v>25.888805625</v>
       </c>
       <c r="Q26">
-        <v>27.2622534</v>
+        <v>27.088805625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1085880327053547</v>
+        <v>0.1092559905000925</v>
       </c>
       <c r="T26">
-        <v>1.258501978185486</v>
+        <v>1.271890297102353</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.260831106077895</v>
+        <v>6.97039786183478</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0921232428750694</v>
+        <v>0.09194558089406921</v>
       </c>
       <c r="C27">
-        <v>332.3467164887363</v>
+        <v>328.878590644584</v>
       </c>
       <c r="D27">
-        <v>371.8217164887363</v>
+        <v>372.612590644584</v>
       </c>
       <c r="E27">
-        <v>53.47499999999999</v>
+        <v>57.73399999999999</v>
       </c>
       <c r="F27">
-        <v>106.475</v>
+        <v>110.734</v>
       </c>
       <c r="G27">
         <v>67</v>
@@ -3489,28 +3489,28 @@
         <v>40.3</v>
       </c>
       <c r="M27">
-        <v>5.781592499999999</v>
+        <v>6.0128562</v>
       </c>
       <c r="N27">
-        <v>34.5184075</v>
+        <v>34.2871438</v>
       </c>
       <c r="O27">
-        <v>8.629601874999999</v>
+        <v>8.571785949999999</v>
       </c>
       <c r="P27">
-        <v>25.888805625</v>
+        <v>25.71535785</v>
       </c>
       <c r="Q27">
-        <v>27.088805625</v>
+        <v>26.91535785</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1092559905000925</v>
+        <v>0.1099420012082016</v>
       </c>
       <c r="T27">
-        <v>1.271890297102353</v>
+        <v>1.285640462476433</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.97039786183478</v>
+        <v>6.702305636379595</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09194558089406921</v>
+        <v>0.09176791891306901</v>
       </c>
       <c r="C28">
-        <v>328.878590644584</v>
+        <v>325.4138363903862</v>
       </c>
       <c r="D28">
-        <v>372.612590644584</v>
+        <v>373.4068363903862</v>
       </c>
       <c r="E28">
-        <v>57.73399999999999</v>
+        <v>61.99299999999999</v>
       </c>
       <c r="F28">
-        <v>110.734</v>
+        <v>114.993</v>
       </c>
       <c r="G28">
         <v>67</v>
@@ -3571,28 +3571,28 @@
         <v>40.3</v>
       </c>
       <c r="M28">
-        <v>6.0128562</v>
+        <v>6.2441199</v>
       </c>
       <c r="N28">
-        <v>34.2871438</v>
+        <v>34.0558801</v>
       </c>
       <c r="O28">
-        <v>8.571785949999999</v>
+        <v>8.513970024999999</v>
       </c>
       <c r="P28">
-        <v>25.71535785</v>
+        <v>25.541910075</v>
       </c>
       <c r="Q28">
-        <v>26.91535785</v>
+        <v>26.741910075</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1099420012082016</v>
+        <v>0.1106468067302315</v>
       </c>
       <c r="T28">
-        <v>1.285640462476433</v>
+        <v>1.299767344710076</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.702305636379595</v>
+        <v>6.454072094291462</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09176791891306901</v>
+        <v>0.09159025693206883</v>
       </c>
       <c r="C29">
-        <v>325.4138363903862</v>
+        <v>321.952475332427</v>
       </c>
       <c r="D29">
-        <v>373.4068363903862</v>
+        <v>374.204475332427</v>
       </c>
       <c r="E29">
-        <v>61.99299999999999</v>
+        <v>66.25200000000001</v>
       </c>
       <c r="F29">
-        <v>114.993</v>
+        <v>119.252</v>
       </c>
       <c r="G29">
         <v>67</v>
@@ -3653,28 +3653,28 @@
         <v>40.3</v>
       </c>
       <c r="M29">
-        <v>6.2441199</v>
+        <v>6.475383600000001</v>
       </c>
       <c r="N29">
-        <v>34.0558801</v>
+        <v>33.8246164</v>
       </c>
       <c r="O29">
-        <v>8.513970024999999</v>
+        <v>8.456154099999999</v>
       </c>
       <c r="P29">
-        <v>25.541910075</v>
+        <v>25.3684623</v>
       </c>
       <c r="Q29">
-        <v>26.741910075</v>
+        <v>26.5684623</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1106468067302315</v>
+        <v>0.1113711901834289</v>
       </c>
       <c r="T29">
-        <v>1.299767344710076</v>
+        <v>1.314286640339098</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.454072094291462</v>
+        <v>6.223569519495338</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09159025693206883</v>
+        <v>0.09163009495106864</v>
       </c>
       <c r="C30">
-        <v>321.952475332427</v>
+        <v>317.5143205846553</v>
       </c>
       <c r="D30">
-        <v>374.204475332427</v>
+        <v>374.0253205846553</v>
       </c>
       <c r="E30">
-        <v>66.25200000000001</v>
+        <v>70.51100000000001</v>
       </c>
       <c r="F30">
-        <v>119.252</v>
+        <v>123.511</v>
       </c>
       <c r="G30">
         <v>67</v>
@@ -3735,45 +3735,45 @@
         <v>40.3</v>
       </c>
       <c r="M30">
-        <v>6.475383600000001</v>
+        <v>6.830158300000001</v>
       </c>
       <c r="N30">
-        <v>33.8246164</v>
+        <v>33.4698417</v>
       </c>
       <c r="O30">
-        <v>8.456154099999999</v>
+        <v>8.367460424999999</v>
       </c>
       <c r="P30">
-        <v>25.3684623</v>
+        <v>25.102381275</v>
       </c>
       <c r="Q30">
-        <v>26.5684623</v>
+        <v>26.302381275</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1113711901834289</v>
+        <v>0.112115978804322</v>
       </c>
       <c r="T30">
-        <v>1.314286640339098</v>
+        <v>1.329214930211192</v>
       </c>
       <c r="U30">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>6.223569519495338</v>
+        <v>5.900302486400643</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09163009495106864</v>
+        <v>0.09145993297006845</v>
       </c>
       <c r="C31">
-        <v>317.5143205846554</v>
+        <v>314.0217535389941</v>
       </c>
       <c r="D31">
-        <v>374.0253205846553</v>
+        <v>374.791753538994</v>
       </c>
       <c r="E31">
-        <v>70.51099999999998</v>
+        <v>74.76999999999998</v>
       </c>
       <c r="F31">
-        <v>123.511</v>
+        <v>127.77</v>
       </c>
       <c r="G31">
         <v>67</v>
@@ -3817,28 +3817,28 @@
         <v>40.3</v>
       </c>
       <c r="M31">
-        <v>6.830158299999999</v>
+        <v>7.065681</v>
       </c>
       <c r="N31">
-        <v>33.4698417</v>
+        <v>33.234319</v>
       </c>
       <c r="O31">
-        <v>8.367460424999999</v>
+        <v>8.30857975</v>
       </c>
       <c r="P31">
-        <v>25.102381275</v>
+        <v>24.92573925</v>
       </c>
       <c r="Q31">
-        <v>26.302381275</v>
+        <v>26.12573925</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.112115978804322</v>
+        <v>0.1128820471000978</v>
       </c>
       <c r="T31">
-        <v>1.329214930211192</v>
+        <v>1.344569742651059</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.900302486400645</v>
+        <v>5.703625736853956</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09145993297006845</v>
+        <v>0.09128977098906828</v>
       </c>
       <c r="C32">
-        <v>314.0217535389941</v>
+        <v>310.5323340110101</v>
       </c>
       <c r="D32">
-        <v>374.791753538994</v>
+        <v>375.56133401101</v>
       </c>
       <c r="E32">
-        <v>74.76999999999998</v>
+        <v>79.029</v>
       </c>
       <c r="F32">
-        <v>127.77</v>
+        <v>132.029</v>
       </c>
       <c r="G32">
         <v>67</v>
@@ -3899,28 +3899,28 @@
         <v>40.3</v>
       </c>
       <c r="M32">
-        <v>7.065681</v>
+        <v>7.3012037</v>
       </c>
       <c r="N32">
-        <v>33.234319</v>
+        <v>32.9987963</v>
       </c>
       <c r="O32">
-        <v>8.30857975</v>
+        <v>8.249699074999999</v>
       </c>
       <c r="P32">
-        <v>24.92573925</v>
+        <v>24.749097225</v>
       </c>
       <c r="Q32">
-        <v>26.12573925</v>
+        <v>25.949097225</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1128820471000978</v>
+        <v>0.113670320274012</v>
       </c>
       <c r="T32">
-        <v>1.344569742651059</v>
+        <v>1.360369622118169</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.703625736853956</v>
+        <v>5.519637809858667</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09128977098906828</v>
+        <v>0.09111960900806809</v>
       </c>
       <c r="C33">
-        <v>310.5323340110101</v>
+        <v>307.0460814295097</v>
       </c>
       <c r="D33">
-        <v>375.56133401101</v>
+        <v>376.3340814295098</v>
       </c>
       <c r="E33">
-        <v>79.029</v>
+        <v>83.28799999999998</v>
       </c>
       <c r="F33">
-        <v>132.029</v>
+        <v>136.288</v>
       </c>
       <c r="G33">
         <v>67</v>
@@ -3981,28 +3981,28 @@
         <v>40.3</v>
       </c>
       <c r="M33">
-        <v>7.3012037</v>
+        <v>7.536726399999999</v>
       </c>
       <c r="N33">
-        <v>32.9987963</v>
+        <v>32.7632736</v>
       </c>
       <c r="O33">
-        <v>8.249699074999999</v>
+        <v>8.190818399999999</v>
       </c>
       <c r="P33">
-        <v>24.749097225</v>
+        <v>24.5724552</v>
       </c>
       <c r="Q33">
-        <v>25.949097225</v>
+        <v>25.7724552</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.113670320274012</v>
+        <v>0.1144817779530413</v>
       </c>
       <c r="T33">
-        <v>1.360369622118169</v>
+        <v>1.376634203922547</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.519637809858667</v>
+        <v>5.347149128300584</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09111960900806809</v>
+        <v>0.09094944702706791</v>
       </c>
       <c r="C34">
-        <v>307.0460814295097</v>
+        <v>303.5630153835345</v>
       </c>
       <c r="D34">
-        <v>376.3340814295098</v>
+        <v>377.1100153835345</v>
       </c>
       <c r="E34">
-        <v>83.28799999999998</v>
+        <v>87.547</v>
       </c>
       <c r="F34">
-        <v>136.288</v>
+        <v>140.547</v>
       </c>
       <c r="G34">
         <v>67</v>
@@ -4063,28 +4063,28 @@
         <v>40.3</v>
       </c>
       <c r="M34">
-        <v>7.536726399999999</v>
+        <v>7.7722491</v>
       </c>
       <c r="N34">
-        <v>32.7632736</v>
+        <v>32.5277509</v>
       </c>
       <c r="O34">
-        <v>8.190818399999999</v>
+        <v>8.131937725</v>
       </c>
       <c r="P34">
-        <v>24.5724552</v>
+        <v>24.395813175</v>
       </c>
       <c r="Q34">
-        <v>25.7724552</v>
+        <v>25.595813175</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1144817779530413</v>
+        <v>0.1153174582493551</v>
       </c>
       <c r="T34">
-        <v>1.376634203922547</v>
+        <v>1.393384295631533</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.347149128300584</v>
+        <v>5.18511430623087</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09094944702706791</v>
+        <v>0.09077928504606772</v>
       </c>
       <c r="C35">
-        <v>303.5630153835345</v>
+        <v>300.0831556240162</v>
       </c>
       <c r="D35">
-        <v>377.1100153835345</v>
+        <v>377.8891556240162</v>
       </c>
       <c r="E35">
-        <v>87.547</v>
+        <v>91.80600000000001</v>
       </c>
       <c r="F35">
-        <v>140.547</v>
+        <v>144.806</v>
       </c>
       <c r="G35">
         <v>67</v>
@@ -4145,28 +4145,28 @@
         <v>40.3</v>
       </c>
       <c r="M35">
-        <v>7.7722491</v>
+        <v>8.0077718</v>
       </c>
       <c r="N35">
-        <v>32.5277509</v>
+        <v>32.2922282</v>
       </c>
       <c r="O35">
-        <v>8.131937725</v>
+        <v>8.073057049999999</v>
       </c>
       <c r="P35">
-        <v>24.395813175</v>
+        <v>24.21917115</v>
       </c>
       <c r="Q35">
-        <v>25.595813175</v>
+        <v>25.41917115</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1153174582493551</v>
+        <v>0.1161784621910117</v>
       </c>
       <c r="T35">
-        <v>1.393384295631533</v>
+        <v>1.410641965877156</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.18511430623087</v>
+        <v>5.032610944282903</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09077928504606772</v>
+        <v>0.09060912306506752</v>
       </c>
       <c r="C36">
-        <v>300.0831556240162</v>
+        <v>296.6065220654527</v>
       </c>
       <c r="D36">
-        <v>377.8891556240162</v>
+        <v>378.6715220654527</v>
       </c>
       <c r="E36">
-        <v>91.80600000000001</v>
+        <v>96.065</v>
       </c>
       <c r="F36">
-        <v>144.806</v>
+        <v>149.065</v>
       </c>
       <c r="G36">
         <v>67</v>
@@ -4227,28 +4227,28 @@
         <v>40.3</v>
       </c>
       <c r="M36">
-        <v>8.0077718</v>
+        <v>8.243294499999999</v>
       </c>
       <c r="N36">
-        <v>32.2922282</v>
+        <v>32.0567055</v>
       </c>
       <c r="O36">
-        <v>8.073057049999999</v>
+        <v>8.014176375</v>
       </c>
       <c r="P36">
-        <v>24.21917115</v>
+        <v>24.042529125</v>
       </c>
       <c r="Q36">
-        <v>25.41917115</v>
+        <v>25.242529125</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1161784621910117</v>
+        <v>0.1170659585616424</v>
       </c>
       <c r="T36">
-        <v>1.410641965877156</v>
+        <v>1.428430641361105</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.032610944282903</v>
+        <v>4.888822060160535</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09060912306506752</v>
+        <v>0.09043896108406733</v>
       </c>
       <c r="C37">
-        <v>296.6065220654527</v>
+        <v>293.1331347876046</v>
       </c>
       <c r="D37">
-        <v>378.6715220654527</v>
+        <v>379.4571347876046</v>
       </c>
       <c r="E37">
-        <v>96.065</v>
+        <v>100.324</v>
       </c>
       <c r="F37">
-        <v>149.065</v>
+        <v>153.324</v>
       </c>
       <c r="G37">
         <v>67</v>
@@ -4309,28 +4309,28 @@
         <v>40.3</v>
       </c>
       <c r="M37">
-        <v>8.243294499999999</v>
+        <v>8.478817200000002</v>
       </c>
       <c r="N37">
-        <v>32.0567055</v>
+        <v>31.8211828</v>
       </c>
       <c r="O37">
-        <v>8.014176375</v>
+        <v>7.955295699999999</v>
       </c>
       <c r="P37">
-        <v>24.042529125</v>
+        <v>23.86588709999999</v>
       </c>
       <c r="Q37">
-        <v>25.242529125</v>
+        <v>25.06588709999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1170659585616424</v>
+        <v>0.1179811891938552</v>
       </c>
       <c r="T37">
-        <v>1.428430641361105</v>
+        <v>1.446775212953927</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.888822060160535</v>
+        <v>4.753021447378296</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09043896108406735</v>
+        <v>0.09026879910306715</v>
       </c>
       <c r="C38">
-        <v>293.1331347876046</v>
+        <v>289.6630140372132</v>
       </c>
       <c r="D38">
-        <v>379.4571347876046</v>
+        <v>380.2460140372132</v>
       </c>
       <c r="E38">
-        <v>100.324</v>
+        <v>104.583</v>
       </c>
       <c r="F38">
-        <v>153.324</v>
+        <v>157.583</v>
       </c>
       <c r="G38">
         <v>67</v>
@@ -4391,28 +4391,28 @@
         <v>40.3</v>
       </c>
       <c r="M38">
-        <v>8.4788172</v>
+        <v>8.714339900000001</v>
       </c>
       <c r="N38">
-        <v>31.8211828</v>
+        <v>31.5856601</v>
       </c>
       <c r="O38">
-        <v>7.955295699999999</v>
+        <v>7.896415025</v>
       </c>
       <c r="P38">
-        <v>23.86588709999999</v>
+        <v>23.689245075</v>
       </c>
       <c r="Q38">
-        <v>25.06588709999999</v>
+        <v>24.889245075</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1179811891938552</v>
+        <v>0.1189254747667733</v>
       </c>
       <c r="T38">
-        <v>1.446775212953927</v>
+        <v>1.465702151898902</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.753021447378297</v>
+        <v>4.624561408259964</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09026879910306715</v>
+        <v>0.09009863712206699</v>
       </c>
       <c r="C39">
-        <v>289.6630140372132</v>
+        <v>286.19618022974</v>
       </c>
       <c r="D39">
-        <v>380.2460140372132</v>
+        <v>381.03818022974</v>
       </c>
       <c r="E39">
-        <v>104.583</v>
+        <v>108.842</v>
       </c>
       <c r="F39">
-        <v>157.583</v>
+        <v>161.842</v>
       </c>
       <c r="G39">
         <v>67</v>
@@ -4473,28 +4473,28 @@
         <v>40.3</v>
       </c>
       <c r="M39">
-        <v>8.714339900000001</v>
+        <v>8.949862599999999</v>
       </c>
       <c r="N39">
-        <v>31.5856601</v>
+        <v>31.3501374</v>
       </c>
       <c r="O39">
-        <v>7.896415025</v>
+        <v>7.837534349999999</v>
       </c>
       <c r="P39">
-        <v>23.689245075</v>
+        <v>23.51260305</v>
       </c>
       <c r="Q39">
-        <v>24.889245075</v>
+        <v>24.71260305</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1189254747667733</v>
+        <v>0.1199002211646242</v>
       </c>
       <c r="T39">
-        <v>1.465702151898902</v>
+        <v>1.485239637261458</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.624561408259964</v>
+        <v>4.50286242383207</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09009863712206699</v>
+        <v>0.09065972514106679</v>
       </c>
       <c r="C40">
-        <v>286.19618022974</v>
+        <v>279.3375268893366</v>
       </c>
       <c r="D40">
-        <v>381.03818022974</v>
+        <v>378.4385268893366</v>
       </c>
       <c r="E40">
-        <v>108.842</v>
+        <v>113.101</v>
       </c>
       <c r="F40">
-        <v>161.842</v>
+        <v>166.101</v>
       </c>
       <c r="G40">
         <v>67</v>
@@ -4555,45 +4555,45 @@
         <v>40.3</v>
       </c>
       <c r="M40">
-        <v>8.949862599999999</v>
+        <v>9.600637800000001</v>
       </c>
       <c r="N40">
-        <v>31.3501374</v>
+        <v>30.6993622</v>
       </c>
       <c r="O40">
-        <v>7.837534349999999</v>
+        <v>7.674840549999999</v>
       </c>
       <c r="P40">
-        <v>23.51260305</v>
+        <v>23.02452165</v>
       </c>
       <c r="Q40">
-        <v>24.71260305</v>
+        <v>24.22452165</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1199002211646242</v>
+        <v>0.1209069264607652</v>
       </c>
       <c r="T40">
-        <v>1.485239637261458</v>
+        <v>1.505417695914589</v>
       </c>
       <c r="U40">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V40">
         <v>0.25</v>
       </c>
       <c r="W40">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>4.50286242383207</v>
+        <v>4.197637786106251</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09065972514106679</v>
+        <v>0.09050831316006661</v>
       </c>
       <c r="C41">
-        <v>279.3375268893366</v>
+        <v>275.7765532902605</v>
       </c>
       <c r="D41">
-        <v>378.4385268893366</v>
+        <v>379.1365532902605</v>
       </c>
       <c r="E41">
-        <v>113.101</v>
+        <v>117.36</v>
       </c>
       <c r="F41">
-        <v>166.101</v>
+        <v>170.36</v>
       </c>
       <c r="G41">
         <v>67</v>
@@ -4637,28 +4637,28 @@
         <v>40.3</v>
       </c>
       <c r="M41">
-        <v>9.600637800000001</v>
+        <v>9.846808000000001</v>
       </c>
       <c r="N41">
-        <v>30.6993622</v>
+        <v>30.45319199999999</v>
       </c>
       <c r="O41">
-        <v>7.674840549999999</v>
+        <v>7.613297999999999</v>
       </c>
       <c r="P41">
-        <v>23.02452165</v>
+        <v>22.83989399999999</v>
       </c>
       <c r="Q41">
-        <v>24.22452165</v>
+        <v>24.03989399999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1209069264607652</v>
+        <v>0.121947188600111</v>
       </c>
       <c r="T41">
-        <v>1.505417695914589</v>
+        <v>1.526268356522824</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.197637786106251</v>
+        <v>4.092696841453595</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09050831316006661</v>
+        <v>0.09143315117906642</v>
       </c>
       <c r="C42">
-        <v>275.7765532902605</v>
+        <v>267.2936685905806</v>
       </c>
       <c r="D42">
-        <v>379.1365532902605</v>
+        <v>374.9126685905807</v>
       </c>
       <c r="E42">
-        <v>117.36</v>
+        <v>121.619</v>
       </c>
       <c r="F42">
-        <v>170.36</v>
+        <v>174.619</v>
       </c>
       <c r="G42">
         <v>67</v>
@@ -4719,45 +4719,45 @@
         <v>40.3</v>
       </c>
       <c r="M42">
-        <v>9.846808000000001</v>
+        <v>10.7041447</v>
       </c>
       <c r="N42">
-        <v>30.45319199999999</v>
+        <v>29.5958553</v>
       </c>
       <c r="O42">
-        <v>7.613297999999999</v>
+        <v>7.398963824999999</v>
       </c>
       <c r="P42">
-        <v>22.83989399999999</v>
+        <v>22.196891475</v>
       </c>
       <c r="Q42">
-        <v>24.03989399999999</v>
+        <v>23.396891475</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.121947188600111</v>
+        <v>0.1230227138628245</v>
       </c>
       <c r="T42">
-        <v>1.526268356522824</v>
+        <v>1.547825819185576</v>
       </c>
       <c r="U42">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V42">
         <v>0.25</v>
       </c>
       <c r="W42">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.092696841453595</v>
+        <v>3.764896788063786</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09143315117906642</v>
+        <v>0.09130798919806625</v>
       </c>
       <c r="C43">
-        <v>267.2936685905806</v>
+        <v>263.6007886697096</v>
       </c>
       <c r="D43">
-        <v>374.9126685905807</v>
+        <v>375.4787886697096</v>
       </c>
       <c r="E43">
-        <v>121.619</v>
+        <v>125.878</v>
       </c>
       <c r="F43">
-        <v>174.619</v>
+        <v>178.878</v>
       </c>
       <c r="G43">
         <v>67</v>
@@ -4801,28 +4801,28 @@
         <v>40.3</v>
       </c>
       <c r="M43">
-        <v>10.7041447</v>
+        <v>10.9652214</v>
       </c>
       <c r="N43">
-        <v>29.5958553</v>
+        <v>29.3347786</v>
       </c>
       <c r="O43">
-        <v>7.398963824999999</v>
+        <v>7.333694649999999</v>
       </c>
       <c r="P43">
-        <v>22.196891475</v>
+        <v>22.00108395</v>
       </c>
       <c r="Q43">
-        <v>23.396891475</v>
+        <v>23.20108395</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1230227138628245</v>
+        <v>0.1241353262035625</v>
       </c>
       <c r="T43">
-        <v>1.547825819185576</v>
+        <v>1.570126642629802</v>
       </c>
       <c r="U43">
         <v>0.0613</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.764896788063786</v>
+        <v>3.675256388347981</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09130798919806626</v>
+        <v>0.09118282721706605</v>
       </c>
       <c r="C44">
-        <v>263.6007886697096</v>
+        <v>259.9096210229081</v>
       </c>
       <c r="D44">
-        <v>375.4787886697096</v>
+        <v>376.0466210229081</v>
       </c>
       <c r="E44">
-        <v>125.878</v>
+        <v>130.137</v>
       </c>
       <c r="F44">
-        <v>178.878</v>
+        <v>183.137</v>
       </c>
       <c r="G44">
         <v>67</v>
@@ -4883,28 +4883,28 @@
         <v>40.3</v>
       </c>
       <c r="M44">
-        <v>10.9652214</v>
+        <v>11.2262981</v>
       </c>
       <c r="N44">
-        <v>29.3347786</v>
+        <v>29.0737019</v>
       </c>
       <c r="O44">
-        <v>7.33369465</v>
+        <v>7.268425474999999</v>
       </c>
       <c r="P44">
-        <v>22.00108395</v>
+        <v>21.805276425</v>
       </c>
       <c r="Q44">
-        <v>23.20108395</v>
+        <v>23.00527642499999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1241353262035625</v>
+        <v>0.1252869775738001</v>
       </c>
       <c r="T44">
-        <v>1.570126642629802</v>
+        <v>1.593209951107158</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.675256388347982</v>
+        <v>3.589785309549191</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09118282721706605</v>
+        <v>0.09105766523606587</v>
       </c>
       <c r="C45">
-        <v>259.9096210229081</v>
+        <v>256.2201734303003</v>
       </c>
       <c r="D45">
-        <v>376.0466210229081</v>
+        <v>376.6161734303003</v>
       </c>
       <c r="E45">
-        <v>130.137</v>
+        <v>134.396</v>
       </c>
       <c r="F45">
-        <v>183.137</v>
+        <v>187.396</v>
       </c>
       <c r="G45">
         <v>67</v>
@@ -4965,28 +4965,28 @@
         <v>40.3</v>
       </c>
       <c r="M45">
-        <v>11.2262981</v>
+        <v>11.4873748</v>
       </c>
       <c r="N45">
-        <v>29.0737019</v>
+        <v>28.8126252</v>
       </c>
       <c r="O45">
-        <v>7.268425474999999</v>
+        <v>7.2031563</v>
       </c>
       <c r="P45">
-        <v>21.805276425</v>
+        <v>21.6094689</v>
       </c>
       <c r="Q45">
-        <v>23.00527642499999</v>
+        <v>22.8094689</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1252869775738001</v>
+        <v>0.1264797593501176</v>
       </c>
       <c r="T45">
-        <v>1.593209951107158</v>
+        <v>1.617117663458706</v>
       </c>
       <c r="U45">
         <v>0.0613</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.589785309549191</v>
+        <v>3.50819927978671</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09105766523606587</v>
+        <v>0.09187750325506569</v>
       </c>
       <c r="C46">
-        <v>256.2201734303003</v>
+        <v>248.2615351229498</v>
       </c>
       <c r="D46">
-        <v>376.6161734303003</v>
+        <v>372.9165351229498</v>
       </c>
       <c r="E46">
-        <v>134.396</v>
+        <v>138.655</v>
       </c>
       <c r="F46">
-        <v>187.396</v>
+        <v>191.655</v>
       </c>
       <c r="G46">
         <v>67</v>
@@ -5047,45 +5047,45 @@
         <v>40.3</v>
       </c>
       <c r="M46">
-        <v>11.4873748</v>
+        <v>12.2850855</v>
       </c>
       <c r="N46">
-        <v>28.8126252</v>
+        <v>28.0149145</v>
       </c>
       <c r="O46">
-        <v>7.2031563</v>
+        <v>7.003728624999999</v>
       </c>
       <c r="P46">
-        <v>21.6094689</v>
+        <v>21.011185875</v>
       </c>
       <c r="Q46">
-        <v>22.8094689</v>
+        <v>22.21118587499999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1264797593501176</v>
+        <v>0.1277159150092103</v>
       </c>
       <c r="T46">
-        <v>1.617117663458706</v>
+        <v>1.641894747168492</v>
       </c>
       <c r="U46">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V46">
         <v>0.25</v>
       </c>
       <c r="W46">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>3.50819927978671</v>
+        <v>3.280400449797439</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09187750325506569</v>
+        <v>0.0917733412740655</v>
       </c>
       <c r="C47">
-        <v>248.2615351229498</v>
+        <v>244.468545395036</v>
       </c>
       <c r="D47">
-        <v>372.9165351229498</v>
+        <v>373.3825453950359</v>
       </c>
       <c r="E47">
-        <v>138.655</v>
+        <v>142.914</v>
       </c>
       <c r="F47">
-        <v>191.655</v>
+        <v>195.914</v>
       </c>
       <c r="G47">
         <v>67</v>
@@ -5129,28 +5129,28 @@
         <v>40.3</v>
       </c>
       <c r="M47">
-        <v>12.2850855</v>
+        <v>12.5580874</v>
       </c>
       <c r="N47">
-        <v>28.0149145</v>
+        <v>27.7419126</v>
       </c>
       <c r="O47">
-        <v>7.003728624999999</v>
+        <v>6.93547815</v>
       </c>
       <c r="P47">
-        <v>21.011185875</v>
+        <v>20.80643445</v>
       </c>
       <c r="Q47">
-        <v>22.21118587499999</v>
+        <v>22.00643445</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1277159150092103</v>
+        <v>0.1289978542112324</v>
       </c>
       <c r="T47">
-        <v>1.641894747168492</v>
+        <v>1.667589500645307</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.280400449797439</v>
+        <v>3.209087396540973</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0917733412740655</v>
+        <v>0.09166917929306531</v>
       </c>
       <c r="C48">
-        <v>244.468545395036</v>
+        <v>240.6767218116659</v>
       </c>
       <c r="D48">
-        <v>373.3825453950359</v>
+        <v>373.8497218116659</v>
       </c>
       <c r="E48">
-        <v>142.914</v>
+        <v>147.173</v>
       </c>
       <c r="F48">
-        <v>195.914</v>
+        <v>200.173</v>
       </c>
       <c r="G48">
         <v>67</v>
@@ -5211,28 +5211,28 @@
         <v>40.3</v>
       </c>
       <c r="M48">
-        <v>12.5580874</v>
+        <v>12.8310893</v>
       </c>
       <c r="N48">
-        <v>27.7419126</v>
+        <v>27.4689107</v>
       </c>
       <c r="O48">
-        <v>6.93547815</v>
+        <v>6.867227674999999</v>
       </c>
       <c r="P48">
-        <v>20.80643445</v>
+        <v>20.601683025</v>
       </c>
       <c r="Q48">
-        <v>22.00643445</v>
+        <v>21.801683025</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1289978542112324</v>
+        <v>0.1303281684774817</v>
       </c>
       <c r="T48">
-        <v>1.667589500645307</v>
+        <v>1.69425386746087</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.209087396540973</v>
+        <v>3.14080894129542</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09166917929306531</v>
+        <v>0.09156501731206512</v>
       </c>
       <c r="C49">
-        <v>240.6767218116659</v>
+        <v>236.886068755565</v>
       </c>
       <c r="D49">
-        <v>373.8497218116659</v>
+        <v>374.318068755565</v>
       </c>
       <c r="E49">
-        <v>147.173</v>
+        <v>151.432</v>
       </c>
       <c r="F49">
-        <v>200.173</v>
+        <v>204.432</v>
       </c>
       <c r="G49">
         <v>67</v>
@@ -5293,28 +5293,28 @@
         <v>40.3</v>
       </c>
       <c r="M49">
-        <v>12.8310893</v>
+        <v>13.1040912</v>
       </c>
       <c r="N49">
-        <v>27.4689107</v>
+        <v>27.19590879999999</v>
       </c>
       <c r="O49">
-        <v>6.867227674999999</v>
+        <v>6.798977199999999</v>
       </c>
       <c r="P49">
-        <v>20.601683025</v>
+        <v>20.39693159999999</v>
       </c>
       <c r="Q49">
-        <v>21.801683025</v>
+        <v>21.59693159999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1303281684774817</v>
+        <v>0.1317096486770483</v>
       </c>
       <c r="T49">
-        <v>1.69425386746087</v>
+        <v>1.721943786846263</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.14080894129542</v>
+        <v>3.075375421685099</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09156501731206512</v>
+        <v>0.09146085533106495</v>
       </c>
       <c r="C50">
-        <v>236.886068755565</v>
+        <v>233.0965906314485</v>
       </c>
       <c r="D50">
-        <v>374.318068755565</v>
+        <v>374.7875906314485</v>
       </c>
       <c r="E50">
-        <v>151.432</v>
+        <v>155.691</v>
       </c>
       <c r="F50">
-        <v>204.432</v>
+        <v>208.691</v>
       </c>
       <c r="G50">
         <v>67</v>
@@ -5375,28 +5375,28 @@
         <v>40.3</v>
       </c>
       <c r="M50">
-        <v>13.1040912</v>
+        <v>13.3770931</v>
       </c>
       <c r="N50">
-        <v>27.1959088</v>
+        <v>26.9229069</v>
       </c>
       <c r="O50">
-        <v>6.798977199999999</v>
+        <v>6.730726724999999</v>
       </c>
       <c r="P50">
-        <v>20.3969316</v>
+        <v>20.192180175</v>
       </c>
       <c r="Q50">
-        <v>21.5969316</v>
+        <v>21.392180175</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1317096486770483</v>
+        <v>0.1331453045707156</v>
       </c>
       <c r="T50">
-        <v>1.721943786846263</v>
+        <v>1.750719585423239</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.075375421685099</v>
+        <v>3.01261265797724</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09146085533106495</v>
+        <v>0.09428169335006475</v>
       </c>
       <c r="C51">
-        <v>233.0965906314485</v>
+        <v>216.5246551735538</v>
       </c>
       <c r="D51">
-        <v>374.7875906314485</v>
+        <v>362.4746551735537</v>
       </c>
       <c r="E51">
-        <v>155.691</v>
+        <v>159.95</v>
       </c>
       <c r="F51">
-        <v>208.691</v>
+        <v>212.95</v>
       </c>
       <c r="G51">
         <v>67</v>
@@ -5457,45 +5457,45 @@
         <v>40.3</v>
       </c>
       <c r="M51">
-        <v>13.3770931</v>
+        <v>15.311105</v>
       </c>
       <c r="N51">
-        <v>26.9229069</v>
+        <v>24.988895</v>
       </c>
       <c r="O51">
-        <v>6.730726724999999</v>
+        <v>6.24722375</v>
       </c>
       <c r="P51">
-        <v>20.192180175</v>
+        <v>18.74167125</v>
       </c>
       <c r="Q51">
-        <v>21.392180175</v>
+        <v>19.94167125</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1331453045707156</v>
+        <v>0.1346383867001295</v>
       </c>
       <c r="T51">
-        <v>1.750719585423239</v>
+        <v>1.780646415943294</v>
       </c>
       <c r="U51">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>3.01261265797724</v>
+        <v>2.632076522236638</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09428169335006475</v>
+        <v>0.09423603136906458</v>
       </c>
       <c r="C52">
-        <v>216.5246551735538</v>
+        <v>212.4585238356851</v>
       </c>
       <c r="D52">
-        <v>362.4746551735537</v>
+        <v>362.6675238356851</v>
       </c>
       <c r="E52">
-        <v>159.95</v>
+        <v>164.209</v>
       </c>
       <c r="F52">
-        <v>212.95</v>
+        <v>217.209</v>
       </c>
       <c r="G52">
         <v>67</v>
@@ -5539,28 +5539,28 @@
         <v>40.3</v>
       </c>
       <c r="M52">
-        <v>15.311105</v>
+        <v>15.6173271</v>
       </c>
       <c r="N52">
-        <v>24.988895</v>
+        <v>24.6826729</v>
       </c>
       <c r="O52">
-        <v>6.24722375</v>
+        <v>6.170668224999999</v>
       </c>
       <c r="P52">
-        <v>18.74167125</v>
+        <v>18.512004675</v>
       </c>
       <c r="Q52">
-        <v>19.94167125</v>
+        <v>19.712004675</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1346383867001295</v>
+        <v>0.1361924109572747</v>
       </c>
       <c r="T52">
-        <v>1.780646415943294</v>
+        <v>1.811794749749883</v>
       </c>
       <c r="U52">
         <v>0.07190000000000001</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.632076522236638</v>
+        <v>2.58046717866337</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09423603136906458</v>
+        <v>0.09419036938806438</v>
       </c>
       <c r="C53">
-        <v>212.4585238356851</v>
+        <v>208.3925978535492</v>
       </c>
       <c r="D53">
-        <v>362.6675238356851</v>
+        <v>362.8605978535492</v>
       </c>
       <c r="E53">
-        <v>164.209</v>
+        <v>168.468</v>
       </c>
       <c r="F53">
-        <v>217.209</v>
+        <v>221.468</v>
       </c>
       <c r="G53">
         <v>67</v>
@@ -5621,28 +5621,28 @@
         <v>40.3</v>
       </c>
       <c r="M53">
-        <v>15.6173271</v>
+        <v>15.9235492</v>
       </c>
       <c r="N53">
-        <v>24.6826729</v>
+        <v>24.3764508</v>
       </c>
       <c r="O53">
-        <v>6.170668224999999</v>
+        <v>6.094112699999999</v>
       </c>
       <c r="P53">
-        <v>18.512004675</v>
+        <v>18.2823381</v>
       </c>
       <c r="Q53">
-        <v>19.712004675</v>
+        <v>19.4823381</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1361924109572747</v>
+        <v>0.1378111862251341</v>
       </c>
       <c r="T53">
-        <v>1.811794749749883</v>
+        <v>1.844240930798412</v>
       </c>
       <c r="U53">
         <v>0.07190000000000001</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.58046717866337</v>
+        <v>2.530842809842921</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09419036938806438</v>
+        <v>0.09569495740706421</v>
       </c>
       <c r="C54">
-        <v>208.3925978535492</v>
+        <v>197.8780477943285</v>
       </c>
       <c r="D54">
-        <v>362.8605978535492</v>
+        <v>356.6050477943285</v>
       </c>
       <c r="E54">
-        <v>168.468</v>
+        <v>172.727</v>
       </c>
       <c r="F54">
-        <v>221.468</v>
+        <v>225.727</v>
       </c>
       <c r="G54">
         <v>67</v>
@@ -5703,45 +5703,45 @@
         <v>40.3</v>
       </c>
       <c r="M54">
-        <v>15.9235492</v>
+        <v>17.1101066</v>
       </c>
       <c r="N54">
-        <v>24.3764508</v>
+        <v>23.1898934</v>
       </c>
       <c r="O54">
-        <v>6.094112699999999</v>
+        <v>5.797473349999999</v>
       </c>
       <c r="P54">
-        <v>18.2823381</v>
+        <v>17.39242005</v>
       </c>
       <c r="Q54">
-        <v>19.4823381</v>
+        <v>18.59242005</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1378111862251341</v>
+        <v>0.1394988455469451</v>
       </c>
       <c r="T54">
-        <v>1.844240930798412</v>
+        <v>1.878067800402198</v>
       </c>
       <c r="U54">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V54">
         <v>0.25</v>
       </c>
       <c r="W54">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.530842809842921</v>
+        <v>2.355333075481832</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09569495740706421</v>
+        <v>0.09567854542606402</v>
       </c>
       <c r="C55">
-        <v>197.8780477943285</v>
+        <v>193.6861193316394</v>
       </c>
       <c r="D55">
-        <v>356.6050477943285</v>
+        <v>356.6721193316394</v>
       </c>
       <c r="E55">
-        <v>172.727</v>
+        <v>176.986</v>
       </c>
       <c r="F55">
-        <v>225.727</v>
+        <v>229.986</v>
       </c>
       <c r="G55">
         <v>67</v>
@@ -5785,28 +5785,28 @@
         <v>40.3</v>
       </c>
       <c r="M55">
-        <v>17.1101066</v>
+        <v>17.4329388</v>
       </c>
       <c r="N55">
-        <v>23.1898934</v>
+        <v>22.86706119999999</v>
       </c>
       <c r="O55">
-        <v>5.797473349999999</v>
+        <v>5.716765299999999</v>
       </c>
       <c r="P55">
-        <v>17.39242005</v>
+        <v>17.1502959</v>
       </c>
       <c r="Q55">
-        <v>18.59242005</v>
+        <v>18.3502959</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1394988455469451</v>
+        <v>0.1412598813610088</v>
       </c>
       <c r="T55">
-        <v>1.878067800402198</v>
+        <v>1.913365403467018</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.355333075481832</v>
+        <v>2.311715796306243</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09567854542606402</v>
+        <v>0.09566213344506384</v>
       </c>
       <c r="C56">
-        <v>193.6861193316394</v>
+        <v>189.4942161037999</v>
       </c>
       <c r="D56">
-        <v>356.6721193316394</v>
+        <v>356.7392161037999</v>
       </c>
       <c r="E56">
-        <v>176.986</v>
+        <v>181.245</v>
       </c>
       <c r="F56">
-        <v>229.986</v>
+        <v>234.245</v>
       </c>
       <c r="G56">
         <v>67</v>
@@ -5867,28 +5867,28 @@
         <v>40.3</v>
       </c>
       <c r="M56">
-        <v>17.4329388</v>
+        <v>17.755771</v>
       </c>
       <c r="N56">
-        <v>22.86706119999999</v>
+        <v>22.54422899999999</v>
       </c>
       <c r="O56">
-        <v>5.716765299999999</v>
+        <v>5.636057249999999</v>
       </c>
       <c r="P56">
-        <v>17.1502959</v>
+        <v>16.90817174999999</v>
       </c>
       <c r="Q56">
-        <v>18.3502959</v>
+        <v>18.10817174999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1412598813610088</v>
+        <v>0.1430991854334752</v>
       </c>
       <c r="T56">
-        <v>1.913365403467018</v>
+        <v>1.950231788890275</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.311715796306243</v>
+        <v>2.269684600009765</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09566213344506384</v>
+        <v>0.09564572146406365</v>
       </c>
       <c r="C57">
-        <v>189.4942161037999</v>
+        <v>185.3023381250543</v>
       </c>
       <c r="D57">
-        <v>356.7392161037999</v>
+        <v>356.8063381250544</v>
       </c>
       <c r="E57">
-        <v>181.245</v>
+        <v>185.504</v>
       </c>
       <c r="F57">
-        <v>234.245</v>
+        <v>238.504</v>
       </c>
       <c r="G57">
         <v>67</v>
@@ -5949,28 +5949,28 @@
         <v>40.3</v>
       </c>
       <c r="M57">
-        <v>17.755771</v>
+        <v>18.0786032</v>
       </c>
       <c r="N57">
-        <v>22.54422899999999</v>
+        <v>22.22139679999999</v>
       </c>
       <c r="O57">
-        <v>5.636057249999999</v>
+        <v>5.555349199999998</v>
       </c>
       <c r="P57">
-        <v>16.90817174999999</v>
+        <v>16.6660476</v>
       </c>
       <c r="Q57">
-        <v>18.10817174999999</v>
+        <v>17.86604759999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1430991854334752</v>
+        <v>0.1450220942365083</v>
       </c>
       <c r="T57">
-        <v>1.950231788890275</v>
+        <v>1.988773919105498</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.269684600009765</v>
+        <v>2.229154517866734</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09564572146406365</v>
+        <v>0.09562930948306346</v>
       </c>
       <c r="C58">
-        <v>185.3023381250543</v>
+        <v>181.1104854096575</v>
       </c>
       <c r="D58">
-        <v>356.8063381250544</v>
+        <v>356.8734854096575</v>
       </c>
       <c r="E58">
-        <v>185.504</v>
+        <v>189.763</v>
       </c>
       <c r="F58">
-        <v>238.504</v>
+        <v>242.763</v>
       </c>
       <c r="G58">
         <v>67</v>
@@ -6031,28 +6031,28 @@
         <v>40.3</v>
       </c>
       <c r="M58">
-        <v>18.0786032</v>
+        <v>18.4014354</v>
       </c>
       <c r="N58">
-        <v>22.22139679999999</v>
+        <v>21.8985646</v>
       </c>
       <c r="O58">
-        <v>5.555349199999998</v>
+        <v>5.474641149999999</v>
       </c>
       <c r="P58">
-        <v>16.6660476</v>
+        <v>16.42392345</v>
       </c>
       <c r="Q58">
-        <v>17.86604759999999</v>
+        <v>17.62392345</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1450220942365083</v>
+        <v>0.1470344406582871</v>
       </c>
       <c r="T58">
-        <v>1.988773919105498</v>
+        <v>2.029108706540034</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.229154517866734</v>
+        <v>2.190046543869072</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09562930948306346</v>
+        <v>0.09561289750206328</v>
       </c>
       <c r="C59">
-        <v>181.1104854096575</v>
+        <v>176.9186579718747</v>
       </c>
       <c r="D59">
-        <v>356.8734854096575</v>
+        <v>356.9406579718747</v>
       </c>
       <c r="E59">
-        <v>189.763</v>
+        <v>194.022</v>
       </c>
       <c r="F59">
-        <v>242.763</v>
+        <v>247.022</v>
       </c>
       <c r="G59">
         <v>67</v>
@@ -6113,28 +6113,28 @@
         <v>40.3</v>
       </c>
       <c r="M59">
-        <v>18.4014354</v>
+        <v>18.7242676</v>
       </c>
       <c r="N59">
-        <v>21.8985646</v>
+        <v>21.57573239999999</v>
       </c>
       <c r="O59">
-        <v>5.474641149999999</v>
+        <v>5.393933099999998</v>
       </c>
       <c r="P59">
-        <v>16.42392345</v>
+        <v>16.18179929999999</v>
       </c>
       <c r="Q59">
-        <v>17.62392345</v>
+        <v>17.38179929999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1470344406582871</v>
+        <v>0.1491426131001507</v>
       </c>
       <c r="T59">
-        <v>2.029108706540034</v>
+        <v>2.071364198138118</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.190046543869072</v>
+        <v>2.152287120698915</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09561289750206328</v>
+        <v>0.09559648552106309</v>
       </c>
       <c r="C60">
-        <v>176.9186579718748</v>
+        <v>172.7268558259827</v>
       </c>
       <c r="D60">
-        <v>356.9406579718747</v>
+        <v>357.0078558259826</v>
       </c>
       <c r="E60">
-        <v>194.022</v>
+        <v>198.281</v>
       </c>
       <c r="F60">
-        <v>247.022</v>
+        <v>251.281</v>
       </c>
       <c r="G60">
         <v>67</v>
@@ -6195,28 +6195,28 @@
         <v>40.3</v>
       </c>
       <c r="M60">
-        <v>18.7242676</v>
+        <v>19.0470998</v>
       </c>
       <c r="N60">
-        <v>21.5757324</v>
+        <v>21.2529002</v>
       </c>
       <c r="O60">
-        <v>5.3939331</v>
+        <v>5.313225049999999</v>
       </c>
       <c r="P60">
-        <v>16.1817993</v>
+        <v>15.93967515</v>
       </c>
       <c r="Q60">
-        <v>17.3817993</v>
+        <v>17.13967515</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1491426131001506</v>
+        <v>0.1513536232221051</v>
       </c>
       <c r="T60">
-        <v>2.071364198138118</v>
+        <v>2.115680933228792</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.152287120698916</v>
+        <v>2.115807677975205</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09559648552106309</v>
+        <v>0.09558007354006291</v>
       </c>
       <c r="C61">
-        <v>172.7268558259827</v>
+        <v>168.5350789862682</v>
       </c>
       <c r="D61">
-        <v>357.0078558259826</v>
+        <v>357.0750789862682</v>
       </c>
       <c r="E61">
-        <v>198.281</v>
+        <v>202.54</v>
       </c>
       <c r="F61">
-        <v>251.281</v>
+        <v>255.54</v>
       </c>
       <c r="G61">
         <v>67</v>
@@ -6277,28 +6277,28 @@
         <v>40.3</v>
       </c>
       <c r="M61">
-        <v>19.0470998</v>
+        <v>19.369932</v>
       </c>
       <c r="N61">
-        <v>21.2529002</v>
+        <v>20.930068</v>
       </c>
       <c r="O61">
-        <v>5.313225049999999</v>
+        <v>5.232517</v>
       </c>
       <c r="P61">
-        <v>15.93967515</v>
+        <v>15.697551</v>
       </c>
       <c r="Q61">
-        <v>17.13967515</v>
+        <v>16.897551</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1513536232221051</v>
+        <v>0.1536751838501573</v>
       </c>
       <c r="T61">
-        <v>2.115680933228792</v>
+        <v>2.162213505074</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.115807677975205</v>
+        <v>2.080544216675619</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09558007354006291</v>
+        <v>0.09556366155906273</v>
       </c>
       <c r="C62">
-        <v>168.5350789862682</v>
+        <v>164.3433274670293</v>
       </c>
       <c r="D62">
-        <v>357.0750789862682</v>
+        <v>357.1423274670293</v>
       </c>
       <c r="E62">
-        <v>202.54</v>
+        <v>206.799</v>
       </c>
       <c r="F62">
-        <v>255.54</v>
+        <v>259.799</v>
       </c>
       <c r="G62">
         <v>67</v>
@@ -6359,28 +6359,28 @@
         <v>40.3</v>
       </c>
       <c r="M62">
-        <v>19.369932</v>
+        <v>19.6927642</v>
       </c>
       <c r="N62">
-        <v>20.930068</v>
+        <v>20.6072358</v>
       </c>
       <c r="O62">
-        <v>5.232517</v>
+        <v>5.151808949999999</v>
       </c>
       <c r="P62">
-        <v>15.697551</v>
+        <v>15.45542685</v>
       </c>
       <c r="Q62">
-        <v>16.897551</v>
+        <v>16.65542685</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1536751838501573</v>
+        <v>0.1561157988693916</v>
       </c>
       <c r="T62">
-        <v>2.162213505074</v>
+        <v>2.21113236265486</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.080544216675619</v>
+        <v>2.046436934435035</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09556366155906273</v>
+        <v>0.09554724957806254</v>
       </c>
       <c r="C63">
-        <v>164.3433274670293</v>
+        <v>160.1516012825746</v>
       </c>
       <c r="D63">
-        <v>357.1423274670293</v>
+        <v>357.2096012825746</v>
       </c>
       <c r="E63">
-        <v>206.799</v>
+        <v>211.058</v>
       </c>
       <c r="F63">
-        <v>259.799</v>
+        <v>264.058</v>
       </c>
       <c r="G63">
         <v>67</v>
@@ -6441,28 +6441,28 @@
         <v>40.3</v>
       </c>
       <c r="M63">
-        <v>19.6927642</v>
+        <v>20.0155964</v>
       </c>
       <c r="N63">
-        <v>20.6072358</v>
+        <v>20.2844036</v>
       </c>
       <c r="O63">
-        <v>5.151808949999999</v>
+        <v>5.071100899999999</v>
       </c>
       <c r="P63">
-        <v>15.45542685</v>
+        <v>15.2133027</v>
       </c>
       <c r="Q63">
-        <v>16.65542685</v>
+        <v>16.4133027</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1561157988693916</v>
+        <v>0.1586848673106909</v>
       </c>
       <c r="T63">
-        <v>2.21113236265486</v>
+        <v>2.262625896950502</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.046436934435035</v>
+        <v>2.013429887105437</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09554724957806254</v>
+        <v>0.1022403375970624</v>
       </c>
       <c r="C64">
-        <v>160.1516012825746</v>
+        <v>130.4096006674303</v>
       </c>
       <c r="D64">
-        <v>357.2096012825746</v>
+        <v>331.7266006674303</v>
       </c>
       <c r="E64">
-        <v>211.058</v>
+        <v>215.317</v>
       </c>
       <c r="F64">
-        <v>264.058</v>
+        <v>268.317</v>
       </c>
       <c r="G64">
         <v>67</v>
@@ -6523,45 +6523,45 @@
         <v>40.3</v>
       </c>
       <c r="M64">
-        <v>20.0155964</v>
+        <v>24.14853</v>
       </c>
       <c r="N64">
-        <v>20.2844036</v>
+        <v>16.15147</v>
       </c>
       <c r="O64">
-        <v>5.071100899999999</v>
+        <v>4.037867499999999</v>
       </c>
       <c r="P64">
-        <v>15.2133027</v>
+        <v>12.1136025</v>
       </c>
       <c r="Q64">
-        <v>16.4133027</v>
+        <v>13.3136025</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1586848673106909</v>
+        <v>0.1613928043163848</v>
       </c>
       <c r="T64">
-        <v>2.262625896950502</v>
+        <v>2.316902865532395</v>
       </c>
       <c r="U64">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V64">
         <v>0.25</v>
       </c>
       <c r="W64">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y64">
-        <v>2.013429887105437</v>
+        <v>1.668838641523935</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1022403375970624</v>
+        <v>0.1023304256160622</v>
       </c>
       <c r="C65">
-        <v>130.4096006674303</v>
+        <v>125.8323777707002</v>
       </c>
       <c r="D65">
-        <v>331.7266006674303</v>
+        <v>331.4083777707002</v>
       </c>
       <c r="E65">
-        <v>215.317</v>
+        <v>219.576</v>
       </c>
       <c r="F65">
-        <v>268.317</v>
+        <v>272.576</v>
       </c>
       <c r="G65">
         <v>67</v>
@@ -6605,28 +6605,28 @@
         <v>40.3</v>
       </c>
       <c r="M65">
-        <v>24.14853</v>
+        <v>24.53184</v>
       </c>
       <c r="N65">
-        <v>16.15147</v>
+        <v>15.76816</v>
       </c>
       <c r="O65">
-        <v>4.037867499999999</v>
+        <v>3.94204</v>
       </c>
       <c r="P65">
-        <v>12.1136025</v>
+        <v>11.82612</v>
       </c>
       <c r="Q65">
-        <v>13.3136025</v>
+        <v>13.02612</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1613928043163848</v>
+        <v>0.1642511822668394</v>
       </c>
       <c r="T65">
-        <v>2.316902865532395</v>
+        <v>2.374195221257726</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.668838641523935</v>
+        <v>1.642763037750124</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1023304256160622</v>
+        <v>0.102420513635062</v>
       </c>
       <c r="C66">
-        <v>125.8323777707002</v>
+        <v>121.2557648266321</v>
       </c>
       <c r="D66">
-        <v>331.4083777707002</v>
+        <v>331.0907648266321</v>
       </c>
       <c r="E66">
-        <v>219.576</v>
+        <v>223.835</v>
       </c>
       <c r="F66">
-        <v>272.576</v>
+        <v>276.835</v>
       </c>
       <c r="G66">
         <v>67</v>
@@ -6687,28 +6687,28 @@
         <v>40.3</v>
       </c>
       <c r="M66">
-        <v>24.53184</v>
+        <v>24.91515</v>
       </c>
       <c r="N66">
-        <v>15.76816</v>
+        <v>15.38485</v>
       </c>
       <c r="O66">
-        <v>3.94204</v>
+        <v>3.8462125</v>
       </c>
       <c r="P66">
-        <v>11.82612</v>
+        <v>11.5386375</v>
       </c>
       <c r="Q66">
-        <v>13.02612</v>
+        <v>12.7386375</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1642511822668394</v>
+        <v>0.1672728961001771</v>
       </c>
       <c r="T66">
-        <v>2.374195221257726</v>
+        <v>2.434761425881648</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.642763037750124</v>
+        <v>1.617489760246276</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.102420513635062</v>
+        <v>0.1025106016540618</v>
       </c>
       <c r="C67">
-        <v>121.2557648266321</v>
+        <v>116.6797600832178</v>
       </c>
       <c r="D67">
-        <v>331.0907648266321</v>
+        <v>330.7737600832178</v>
       </c>
       <c r="E67">
-        <v>223.835</v>
+        <v>228.094</v>
       </c>
       <c r="F67">
-        <v>276.835</v>
+        <v>281.094</v>
       </c>
       <c r="G67">
         <v>67</v>
@@ -6769,28 +6769,28 @@
         <v>40.3</v>
       </c>
       <c r="M67">
-        <v>24.91515</v>
+        <v>25.29846</v>
       </c>
       <c r="N67">
-        <v>15.38485</v>
+        <v>15.00154</v>
       </c>
       <c r="O67">
-        <v>3.8462125</v>
+        <v>3.750385</v>
       </c>
       <c r="P67">
-        <v>11.5386375</v>
+        <v>11.251155</v>
       </c>
       <c r="Q67">
-        <v>12.7386375</v>
+        <v>12.451155</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1672728961001771</v>
+        <v>0.1704723578060641</v>
       </c>
       <c r="T67">
-        <v>2.434761425881648</v>
+        <v>2.498890348424624</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.617489760246276</v>
+        <v>1.592982339636484</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1025106016540618</v>
+        <v>0.1026006896730616</v>
       </c>
       <c r="C68">
-        <v>116.6797600832178</v>
+        <v>112.104361795153</v>
       </c>
       <c r="D68">
-        <v>330.7737600832178</v>
+        <v>330.457361795153</v>
       </c>
       <c r="E68">
-        <v>228.094</v>
+        <v>232.353</v>
       </c>
       <c r="F68">
-        <v>281.094</v>
+        <v>285.353</v>
       </c>
       <c r="G68">
         <v>67</v>
@@ -6851,28 +6851,28 @@
         <v>40.3</v>
       </c>
       <c r="M68">
-        <v>25.29846</v>
+        <v>25.68177</v>
       </c>
       <c r="N68">
-        <v>15.00154</v>
+        <v>14.61823</v>
       </c>
       <c r="O68">
-        <v>3.750385</v>
+        <v>3.654557499999999</v>
       </c>
       <c r="P68">
-        <v>11.251155</v>
+        <v>10.9636725</v>
       </c>
       <c r="Q68">
-        <v>12.451155</v>
+        <v>12.1636725</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1704723578060641</v>
+        <v>0.1738657262820049</v>
       </c>
       <c r="T68">
-        <v>2.498890348424624</v>
+        <v>2.56690587233384</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.592982339636484</v>
+        <v>1.569206483821014</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1026006896730616</v>
+        <v>0.1026907776920614</v>
       </c>
       <c r="C69">
-        <v>112.104361795153</v>
+        <v>107.5295682238045</v>
       </c>
       <c r="D69">
-        <v>330.457361795153</v>
+        <v>330.1415682238045</v>
       </c>
       <c r="E69">
-        <v>232.353</v>
+        <v>236.612</v>
       </c>
       <c r="F69">
-        <v>285.353</v>
+        <v>289.612</v>
       </c>
       <c r="G69">
         <v>67</v>
@@ -6933,28 +6933,28 @@
         <v>40.3</v>
       </c>
       <c r="M69">
-        <v>25.68177</v>
+        <v>26.06508</v>
       </c>
       <c r="N69">
-        <v>14.61823</v>
+        <v>14.23492</v>
       </c>
       <c r="O69">
-        <v>3.654557499999999</v>
+        <v>3.558729999999999</v>
       </c>
       <c r="P69">
-        <v>10.9636725</v>
+        <v>10.67619</v>
       </c>
       <c r="Q69">
-        <v>12.1636725</v>
+        <v>11.87619</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1738657262820049</v>
+        <v>0.177471180287692</v>
       </c>
       <c r="T69">
-        <v>2.56690587233384</v>
+        <v>2.639172366487383</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.569206483821014</v>
+        <v>1.546129917882469</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1026907776920614</v>
+        <v>0.1027808657110613</v>
       </c>
       <c r="C70">
-        <v>107.5295682238045</v>
+        <v>102.955377637179</v>
       </c>
       <c r="D70">
-        <v>330.1415682238045</v>
+        <v>329.826377637179</v>
       </c>
       <c r="E70">
-        <v>236.612</v>
+        <v>240.871</v>
       </c>
       <c r="F70">
-        <v>289.612</v>
+        <v>293.871</v>
       </c>
       <c r="G70">
         <v>67</v>
@@ -7015,28 +7015,28 @@
         <v>40.3</v>
       </c>
       <c r="M70">
-        <v>26.06508</v>
+        <v>26.44839</v>
       </c>
       <c r="N70">
-        <v>14.23492</v>
+        <v>13.85161</v>
       </c>
       <c r="O70">
-        <v>3.558729999999999</v>
+        <v>3.4629025</v>
       </c>
       <c r="P70">
-        <v>10.67619</v>
+        <v>10.3887075</v>
       </c>
       <c r="Q70">
-        <v>11.87619</v>
+        <v>11.5887075</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.177471180287692</v>
+        <v>0.1813092442292299</v>
       </c>
       <c r="T70">
-        <v>2.639172366487383</v>
+        <v>2.716101215102445</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.546129917882469</v>
+        <v>1.523722237913159</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1027808657110613</v>
+        <v>0.1028709537300611</v>
       </c>
       <c r="C71">
-        <v>102.955377637179</v>
+        <v>98.38178830989057</v>
       </c>
       <c r="D71">
-        <v>329.826377637179</v>
+        <v>329.5117883098906</v>
       </c>
       <c r="E71">
-        <v>240.871</v>
+        <v>245.13</v>
       </c>
       <c r="F71">
-        <v>293.871</v>
+        <v>298.13</v>
       </c>
       <c r="G71">
         <v>67</v>
@@ -7097,28 +7097,28 @@
         <v>40.3</v>
       </c>
       <c r="M71">
-        <v>26.44839</v>
+        <v>26.8317</v>
       </c>
       <c r="N71">
-        <v>13.85161</v>
+        <v>13.4683</v>
       </c>
       <c r="O71">
-        <v>3.4629025</v>
+        <v>3.367075</v>
       </c>
       <c r="P71">
-        <v>10.3887075</v>
+        <v>10.101225</v>
       </c>
       <c r="Q71">
-        <v>11.5887075</v>
+        <v>11.301225</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1813092442292299</v>
+        <v>0.1854031791002035</v>
       </c>
       <c r="T71">
-        <v>2.716101215102445</v>
+        <v>2.798158653625177</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.523722237913159</v>
+        <v>1.501954777371542</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1028709537300611</v>
+        <v>0.1364386153249725</v>
       </c>
       <c r="C72">
-        <v>98.38178830989057</v>
+        <v>7.722065222270317</v>
       </c>
       <c r="D72">
-        <v>329.5117883098906</v>
+        <v>243.1110652222704</v>
       </c>
       <c r="E72">
-        <v>245.13</v>
+        <v>249.389</v>
       </c>
       <c r="F72">
-        <v>298.13</v>
+        <v>302.389</v>
       </c>
       <c r="G72">
         <v>67</v>
@@ -7179,45 +7179,45 @@
         <v>40.3</v>
       </c>
       <c r="M72">
-        <v>26.8317</v>
+        <v>44.39070520000001</v>
       </c>
       <c r="N72">
-        <v>13.4683</v>
+        <v>-4.090705200000009</v>
       </c>
       <c r="O72">
-        <v>3.367075</v>
+        <v>-1.022676300000002</v>
       </c>
       <c r="P72">
-        <v>10.101225</v>
+        <v>-3.068028900000007</v>
       </c>
       <c r="Q72">
-        <v>11.301225</v>
+        <v>-1.868028900000007</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1854031791002035</v>
+        <v>0.1926427692019803</v>
       </c>
       <c r="T72">
-        <v>2.798158653625177</v>
+        <v>2.94326653599973</v>
       </c>
       <c r="U72">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.25</v>
+        <v>0.2269619271558677</v>
       </c>
       <c r="W72">
-        <v>0.0675</v>
+        <v>0.1134819890935186</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y72">
-        <v>1.501954777371542</v>
+        <v>0.9078477086234709</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1364386153249725</v>
+        <v>0.1374486153249725</v>
       </c>
       <c r="C73">
-        <v>7.722065222270373</v>
+        <v>1.560066338255126</v>
       </c>
       <c r="D73">
-        <v>243.1110652222704</v>
+        <v>241.2080663382551</v>
       </c>
       <c r="E73">
-        <v>249.389</v>
+        <v>253.648</v>
       </c>
       <c r="F73">
-        <v>302.389</v>
+        <v>306.648</v>
       </c>
       <c r="G73">
         <v>67</v>
@@ -7261,37 +7261,37 @@
         <v>40.3</v>
       </c>
       <c r="M73">
-        <v>44.3907052</v>
+        <v>45.0159264</v>
       </c>
       <c r="N73">
-        <v>-4.090705200000002</v>
+        <v>-4.715926400000001</v>
       </c>
       <c r="O73">
-        <v>-1.022676300000001</v>
+        <v>-1.1789816</v>
       </c>
       <c r="P73">
-        <v>-3.068028900000002</v>
+        <v>-3.536944800000001</v>
       </c>
       <c r="Q73">
-        <v>-1.868028900000002</v>
+        <v>-2.3369448</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1926427692019803</v>
+        <v>0.1978871538163367</v>
       </c>
       <c r="T73">
-        <v>2.943266535999729</v>
+        <v>3.048383197999719</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.2269619271558677</v>
+        <v>0.2238096781675918</v>
       </c>
       <c r="W73">
-        <v>0.1134819890935186</v>
+        <v>0.1139447392449975</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.907847708623471</v>
+        <v>0.8952387126703673</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1374486153249725</v>
+        <v>0.1384586153249725</v>
       </c>
       <c r="C74">
-        <v>1.560066338255126</v>
+        <v>-4.572371754907067</v>
       </c>
       <c r="D74">
-        <v>241.2080663382551</v>
+        <v>239.3346282450929</v>
       </c>
       <c r="E74">
-        <v>253.648</v>
+        <v>257.907</v>
       </c>
       <c r="F74">
-        <v>306.648</v>
+        <v>310.907</v>
       </c>
       <c r="G74">
         <v>67</v>
@@ -7343,37 +7343,37 @@
         <v>40.3</v>
       </c>
       <c r="M74">
-        <v>45.0159264</v>
+        <v>45.6411476</v>
       </c>
       <c r="N74">
-        <v>-4.715926400000001</v>
+        <v>-5.341147600000006</v>
       </c>
       <c r="O74">
-        <v>-1.1789816</v>
+        <v>-1.335286900000002</v>
       </c>
       <c r="P74">
-        <v>-3.536944800000001</v>
+        <v>-4.005860700000005</v>
       </c>
       <c r="Q74">
-        <v>-2.3369448</v>
+        <v>-2.805860700000005</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1978871538163367</v>
+        <v>0.2035200113650899</v>
       </c>
       <c r="T74">
-        <v>3.048383197999719</v>
+        <v>3.161286279407116</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.2238096781675918</v>
+        <v>0.220743792165296</v>
       </c>
       <c r="W74">
-        <v>0.1139447392449975</v>
+        <v>0.1143948113101346</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8952387126703673</v>
+        <v>0.882975168661184</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1384586153249725</v>
+        <v>0.1394686153249725</v>
       </c>
       <c r="C75">
-        <v>-4.572371754907067</v>
+        <v>-10.67593253552246</v>
       </c>
       <c r="D75">
-        <v>239.3346282450929</v>
+        <v>237.4900674644776</v>
       </c>
       <c r="E75">
-        <v>257.907</v>
+        <v>262.166</v>
       </c>
       <c r="F75">
-        <v>310.907</v>
+        <v>315.166</v>
       </c>
       <c r="G75">
         <v>67</v>
@@ -7425,37 +7425,37 @@
         <v>40.3</v>
       </c>
       <c r="M75">
-        <v>45.6411476</v>
+        <v>46.2663688</v>
       </c>
       <c r="N75">
-        <v>-5.341147600000006</v>
+        <v>-5.966368800000005</v>
       </c>
       <c r="O75">
-        <v>-1.335286900000002</v>
+        <v>-1.491592200000001</v>
       </c>
       <c r="P75">
-        <v>-4.005860700000005</v>
+        <v>-4.474776600000004</v>
       </c>
       <c r="Q75">
-        <v>-2.805860700000005</v>
+        <v>-3.274776600000004</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2035200113650899</v>
+        <v>0.2095861656483626</v>
       </c>
       <c r="T75">
-        <v>3.161286279407116</v>
+        <v>3.282874213230467</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.220743792165296</v>
+        <v>0.2177607679468461</v>
       </c>
       <c r="W75">
-        <v>0.1143948113101346</v>
+        <v>0.114832719265403</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.882975168661184</v>
+        <v>0.8710430717873843</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1394686153249725</v>
+        <v>0.1404786153249725</v>
       </c>
       <c r="C76">
-        <v>-10.67593253552246</v>
+        <v>-16.75127857267557</v>
       </c>
       <c r="D76">
-        <v>237.4900674644776</v>
+        <v>235.6737214273244</v>
       </c>
       <c r="E76">
-        <v>262.166</v>
+        <v>266.425</v>
       </c>
       <c r="F76">
-        <v>315.166</v>
+        <v>319.425</v>
       </c>
       <c r="G76">
         <v>67</v>
@@ -7507,37 +7507,37 @@
         <v>40.3</v>
       </c>
       <c r="M76">
-        <v>46.2663688</v>
+        <v>46.89159</v>
       </c>
       <c r="N76">
-        <v>-5.966368800000005</v>
+        <v>-6.591590000000004</v>
       </c>
       <c r="O76">
-        <v>-1.491592200000001</v>
+        <v>-1.647897500000001</v>
       </c>
       <c r="P76">
-        <v>-4.474776600000004</v>
+        <v>-4.943692500000003</v>
       </c>
       <c r="Q76">
-        <v>-3.274776600000004</v>
+        <v>-3.743692500000003</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2095861656483626</v>
+        <v>0.2161376122742971</v>
       </c>
       <c r="T76">
-        <v>3.282874213230467</v>
+        <v>3.414189181759685</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.2177607679468461</v>
+        <v>0.2148572910408881</v>
       </c>
       <c r="W76">
-        <v>0.114832719265403</v>
+        <v>0.1152589496751976</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8710430717873843</v>
+        <v>0.8594291641635525</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1404786153249725</v>
+        <v>0.1414886153249725</v>
       </c>
       <c r="C77">
-        <v>-16.75127857267557</v>
+        <v>-22.79905231973919</v>
       </c>
       <c r="D77">
-        <v>235.6737214273244</v>
+        <v>233.8849476802608</v>
       </c>
       <c r="E77">
-        <v>266.425</v>
+        <v>270.684</v>
       </c>
       <c r="F77">
-        <v>319.425</v>
+        <v>323.684</v>
       </c>
       <c r="G77">
         <v>67</v>
@@ -7589,37 +7589,37 @@
         <v>40.3</v>
       </c>
       <c r="M77">
-        <v>46.89159</v>
+        <v>47.5168112</v>
       </c>
       <c r="N77">
-        <v>-6.591590000000004</v>
+        <v>-7.216811200000002</v>
       </c>
       <c r="O77">
-        <v>-1.647897500000001</v>
+        <v>-1.804202800000001</v>
       </c>
       <c r="P77">
-        <v>-4.943692500000003</v>
+        <v>-5.412608400000002</v>
       </c>
       <c r="Q77">
-        <v>-3.743692500000003</v>
+        <v>-4.212608400000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2161376122742971</v>
+        <v>0.2232350127857262</v>
       </c>
       <c r="T77">
-        <v>3.414189181759685</v>
+        <v>3.556447064333006</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.2148572910408881</v>
+        <v>0.2120302214219291</v>
       </c>
       <c r="W77">
-        <v>0.1152589496751976</v>
+        <v>0.1156739634952608</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8594291641635525</v>
+        <v>0.8481208856877163</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1414886153249725</v>
+        <v>0.1424986153249725</v>
       </c>
       <c r="C78">
-        <v>-22.79905231973919</v>
+        <v>-28.81987687201877</v>
       </c>
       <c r="D78">
-        <v>233.8849476802608</v>
+        <v>232.1231231279812</v>
       </c>
       <c r="E78">
-        <v>270.684</v>
+        <v>274.943</v>
       </c>
       <c r="F78">
-        <v>323.684</v>
+        <v>327.943</v>
       </c>
       <c r="G78">
         <v>67</v>
@@ -7671,37 +7671,37 @@
         <v>40.3</v>
       </c>
       <c r="M78">
-        <v>47.5168112</v>
+        <v>48.14203240000001</v>
       </c>
       <c r="N78">
-        <v>-7.216811200000002</v>
+        <v>-7.842032400000008</v>
       </c>
       <c r="O78">
-        <v>-1.804202800000001</v>
+        <v>-1.960508100000002</v>
       </c>
       <c r="P78">
-        <v>-5.412608400000002</v>
+        <v>-5.881524300000006</v>
       </c>
       <c r="Q78">
-        <v>-4.212608400000001</v>
+        <v>-4.681524300000006</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2232350127857262</v>
+        <v>0.2309495785590187</v>
       </c>
       <c r="T78">
-        <v>3.556447064333006</v>
+        <v>3.711075197564876</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.2120302214219291</v>
+        <v>0.2092765821826832</v>
       </c>
       <c r="W78">
-        <v>0.1156739634952608</v>
+        <v>0.1160781977355821</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8481208856877163</v>
+        <v>0.8371063287307329</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1424986153249725</v>
+        <v>0.1435086153249725</v>
       </c>
       <c r="C79">
-        <v>-28.81987687201877</v>
+        <v>-34.81435669041031</v>
       </c>
       <c r="D79">
-        <v>232.1231231279812</v>
+        <v>230.3876433095897</v>
       </c>
       <c r="E79">
-        <v>274.943</v>
+        <v>279.202</v>
       </c>
       <c r="F79">
-        <v>327.943</v>
+        <v>332.202</v>
       </c>
       <c r="G79">
         <v>67</v>
@@ -7753,37 +7753,37 @@
         <v>40.3</v>
       </c>
       <c r="M79">
-        <v>48.14203240000001</v>
+        <v>48.7672536</v>
       </c>
       <c r="N79">
-        <v>-7.842032400000008</v>
+        <v>-8.467253600000006</v>
       </c>
       <c r="O79">
-        <v>-1.960508100000002</v>
+        <v>-2.116813400000002</v>
       </c>
       <c r="P79">
-        <v>-5.881524300000006</v>
+        <v>-6.350440200000005</v>
       </c>
       <c r="Q79">
-        <v>-4.681524300000006</v>
+        <v>-5.150440200000005</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2309495785590187</v>
+        <v>0.2393654684935195</v>
       </c>
       <c r="T79">
-        <v>3.711075197564876</v>
+        <v>3.879760433817825</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.2092765821826832</v>
+        <v>0.206593549077777</v>
       </c>
       <c r="W79">
-        <v>0.1160781977355821</v>
+        <v>0.1164720669953823</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8371063287307329</v>
+        <v>0.8263741963111081</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1435086153249725</v>
+        <v>0.1445186153249725</v>
       </c>
       <c r="C80">
-        <v>-34.81435669041031</v>
+        <v>-40.78307829283631</v>
       </c>
       <c r="D80">
-        <v>230.3876433095897</v>
+        <v>228.6779217071637</v>
       </c>
       <c r="E80">
-        <v>279.202</v>
+        <v>283.461</v>
       </c>
       <c r="F80">
-        <v>332.202</v>
+        <v>336.461</v>
       </c>
       <c r="G80">
         <v>67</v>
@@ -7835,37 +7835,37 @@
         <v>40.3</v>
       </c>
       <c r="M80">
-        <v>48.7672536</v>
+        <v>49.39247480000001</v>
       </c>
       <c r="N80">
-        <v>-8.467253600000006</v>
+        <v>-9.092474800000012</v>
       </c>
       <c r="O80">
-        <v>-2.116813400000002</v>
+        <v>-2.273118700000003</v>
       </c>
       <c r="P80">
-        <v>-6.350440200000005</v>
+        <v>-6.819356100000009</v>
       </c>
       <c r="Q80">
-        <v>-5.150440200000005</v>
+        <v>-5.619356100000009</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2393654684935195</v>
+        <v>0.2485828717551157</v>
       </c>
       <c r="T80">
-        <v>3.879760433817825</v>
+        <v>4.064510930666294</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.206593549077777</v>
+        <v>0.2039784408616026</v>
       </c>
       <c r="W80">
-        <v>0.1164720669953823</v>
+        <v>0.1168559648815168</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8263741963111081</v>
+        <v>0.8159137634464104</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1445186153249725</v>
+        <v>0.1455286153249725</v>
       </c>
       <c r="C81">
-        <v>-40.78307829283631</v>
+        <v>-46.72661091512111</v>
       </c>
       <c r="D81">
-        <v>228.6779217071637</v>
+        <v>226.9933890848789</v>
       </c>
       <c r="E81">
-        <v>283.461</v>
+        <v>287.72</v>
       </c>
       <c r="F81">
-        <v>336.461</v>
+        <v>340.72</v>
       </c>
       <c r="G81">
         <v>67</v>
@@ -7917,37 +7917,37 @@
         <v>40.3</v>
       </c>
       <c r="M81">
-        <v>49.39247480000001</v>
+        <v>50.01769600000001</v>
       </c>
       <c r="N81">
-        <v>-9.092474800000012</v>
+        <v>-9.717696000000011</v>
       </c>
       <c r="O81">
-        <v>-2.273118700000003</v>
+        <v>-2.429424000000003</v>
       </c>
       <c r="P81">
-        <v>-6.819356100000009</v>
+        <v>-7.288272000000008</v>
       </c>
       <c r="Q81">
-        <v>-5.619356100000009</v>
+        <v>-6.088272000000008</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2485828717551157</v>
+        <v>0.2587220153428715</v>
       </c>
       <c r="T81">
-        <v>4.064510930666294</v>
+        <v>4.267736477199608</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.2039784408616026</v>
+        <v>0.2014287103508326</v>
       </c>
       <c r="W81">
-        <v>0.1168559648815168</v>
+        <v>0.1172302653204978</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8159137634464104</v>
+        <v>0.8057148414033304</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1455286153249725</v>
+        <v>0.1924785208224874</v>
       </c>
       <c r="C82">
-        <v>-46.72661091512111</v>
+        <v>-108.8872598168685</v>
       </c>
       <c r="D82">
-        <v>226.9933890848789</v>
+        <v>169.0917401831315</v>
       </c>
       <c r="E82">
-        <v>287.72</v>
+        <v>291.979</v>
       </c>
       <c r="F82">
-        <v>340.72</v>
+        <v>344.979</v>
       </c>
       <c r="G82">
         <v>67</v>
@@ -7999,45 +7999,45 @@
         <v>40.3</v>
       </c>
       <c r="M82">
-        <v>50.01769600000001</v>
+        <v>69.2717832</v>
       </c>
       <c r="N82">
-        <v>-9.717696000000011</v>
+        <v>-28.9717832</v>
       </c>
       <c r="O82">
-        <v>-2.429424000000003</v>
+        <v>-7.242945800000001</v>
       </c>
       <c r="P82">
-        <v>-7.288272000000008</v>
+        <v>-21.7288374</v>
       </c>
       <c r="Q82">
-        <v>-6.088272000000008</v>
+        <v>-20.5288374</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2587220153428715</v>
+        <v>0.2815068871899429</v>
       </c>
       <c r="T82">
-        <v>4.267736477199608</v>
+        <v>4.724428701127128</v>
       </c>
       <c r="U82">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.2014287103508326</v>
+        <v>0.1454416146746458</v>
       </c>
       <c r="W82">
-        <v>0.1172302653204978</v>
+        <v>0.1715953237733311</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.8057148414033304</v>
+        <v>0.581766458698583</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1924785208224874</v>
+        <v>0.1940285208224874</v>
       </c>
       <c r="C83">
-        <v>-108.8872598168685</v>
+        <v>-114.5583262152438</v>
       </c>
       <c r="D83">
-        <v>169.0917401831315</v>
+        <v>167.6796737847562</v>
       </c>
       <c r="E83">
-        <v>291.979</v>
+        <v>296.238</v>
       </c>
       <c r="F83">
-        <v>344.979</v>
+        <v>349.238</v>
       </c>
       <c r="G83">
         <v>67</v>
@@ -8081,37 +8081,37 @@
         <v>40.3</v>
       </c>
       <c r="M83">
-        <v>69.2717832</v>
+        <v>70.1269904</v>
       </c>
       <c r="N83">
-        <v>-28.9717832</v>
+        <v>-29.8269904</v>
       </c>
       <c r="O83">
-        <v>-7.242945800000001</v>
+        <v>-7.4567476</v>
       </c>
       <c r="P83">
-        <v>-21.7288374</v>
+        <v>-22.3702428</v>
       </c>
       <c r="Q83">
-        <v>-20.5288374</v>
+        <v>-21.1702428</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2815068871899429</v>
+        <v>0.2946017142560509</v>
       </c>
       <c r="T83">
-        <v>4.724428701127128</v>
+        <v>4.986896962300857</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1454416146746458</v>
+        <v>0.1436679364469062</v>
       </c>
       <c r="W83">
-        <v>0.1715953237733311</v>
+        <v>0.1719514783614612</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.581766458698583</v>
+        <v>0.5746717457876247</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1940285208224874</v>
+        <v>0.1955785208224874</v>
       </c>
       <c r="C84">
-        <v>-114.5583262152438</v>
+        <v>-120.2060039098313</v>
       </c>
       <c r="D84">
-        <v>167.6796737847562</v>
+        <v>166.2909960901687</v>
       </c>
       <c r="E84">
-        <v>296.238</v>
+        <v>300.497</v>
       </c>
       <c r="F84">
-        <v>349.238</v>
+        <v>353.497</v>
       </c>
       <c r="G84">
         <v>67</v>
@@ -8163,37 +8163,37 @@
         <v>40.3</v>
       </c>
       <c r="M84">
-        <v>70.1269904</v>
+        <v>70.98219760000001</v>
       </c>
       <c r="N84">
-        <v>-29.8269904</v>
+        <v>-30.68219760000001</v>
       </c>
       <c r="O84">
-        <v>-7.4567476</v>
+        <v>-7.670549400000002</v>
       </c>
       <c r="P84">
-        <v>-22.3702428</v>
+        <v>-23.01164820000001</v>
       </c>
       <c r="Q84">
-        <v>-21.1702428</v>
+        <v>-21.81164820000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2946017142560509</v>
+        <v>0.3092371092122893</v>
       </c>
       <c r="T84">
-        <v>4.986896962300857</v>
+        <v>5.280243842436202</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1436679364469062</v>
+        <v>0.1419369974535699</v>
       </c>
       <c r="W84">
-        <v>0.1719514783614612</v>
+        <v>0.1722990509113232</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5746717457876247</v>
+        <v>0.5677479898142798</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1955785208224874</v>
+        <v>0.1971285208224874</v>
       </c>
       <c r="C85">
-        <v>-120.2060039098313</v>
+        <v>-125.8308692244249</v>
       </c>
       <c r="D85">
-        <v>166.2909960901687</v>
+        <v>164.9251307755752</v>
       </c>
       <c r="E85">
-        <v>300.497</v>
+        <v>304.756</v>
       </c>
       <c r="F85">
-        <v>353.497</v>
+        <v>357.756</v>
       </c>
       <c r="G85">
         <v>67</v>
@@ -8245,37 +8245,37 @@
         <v>40.3</v>
       </c>
       <c r="M85">
-        <v>70.98219760000001</v>
+        <v>71.8374048</v>
       </c>
       <c r="N85">
-        <v>-30.68219760000001</v>
+        <v>-31.5374048</v>
       </c>
       <c r="O85">
-        <v>-7.670549400000002</v>
+        <v>-7.884351200000001</v>
       </c>
       <c r="P85">
-        <v>-23.01164820000001</v>
+        <v>-23.6530536</v>
       </c>
       <c r="Q85">
-        <v>-21.81164820000001</v>
+        <v>-22.4530536</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3092371092122893</v>
+        <v>0.3257019285380574</v>
       </c>
       <c r="T85">
-        <v>5.280243842436202</v>
+        <v>5.610259082588466</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1419369974535699</v>
+        <v>0.1402472712934084</v>
       </c>
       <c r="W85">
-        <v>0.1722990509113232</v>
+        <v>0.1726383479242836</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5677479898142798</v>
+        <v>0.5609890851736337</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1971285208224874</v>
+        <v>0.1986785208224874</v>
       </c>
       <c r="C86">
-        <v>-125.8308692244248</v>
+        <v>-131.4334797020618</v>
       </c>
       <c r="D86">
-        <v>164.9251307755752</v>
+        <v>163.5815202979382</v>
       </c>
       <c r="E86">
-        <v>304.756</v>
+        <v>309.015</v>
       </c>
       <c r="F86">
-        <v>357.756</v>
+        <v>362.015</v>
       </c>
       <c r="G86">
         <v>67</v>
@@ -8327,37 +8327,37 @@
         <v>40.3</v>
       </c>
       <c r="M86">
-        <v>71.8374048</v>
+        <v>72.692612</v>
       </c>
       <c r="N86">
-        <v>-31.5374048</v>
+        <v>-32.392612</v>
       </c>
       <c r="O86">
-        <v>-7.884351200000001</v>
+        <v>-8.098153</v>
       </c>
       <c r="P86">
-        <v>-23.6530536</v>
+        <v>-24.294459</v>
       </c>
       <c r="Q86">
-        <v>-22.4530536</v>
+        <v>-23.094459</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3257019285380571</v>
+        <v>0.344362057107261</v>
       </c>
       <c r="T86">
-        <v>5.610259082588462</v>
+        <v>5.984276354761026</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1402472712934084</v>
+        <v>0.1385973033958389</v>
       </c>
       <c r="W86">
-        <v>0.1726383479242836</v>
+        <v>0.1729696614781156</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5609890851736337</v>
+        <v>0.5543892135833557</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1986785208224874</v>
+        <v>0.2002285208224874</v>
       </c>
       <c r="C87">
-        <v>-131.4334797020618</v>
+        <v>-137.0143748638552</v>
       </c>
       <c r="D87">
-        <v>163.5815202979382</v>
+        <v>162.2596251361448</v>
       </c>
       <c r="E87">
-        <v>309.015</v>
+        <v>313.274</v>
       </c>
       <c r="F87">
-        <v>362.015</v>
+        <v>366.274</v>
       </c>
       <c r="G87">
         <v>67</v>
@@ -8409,37 +8409,37 @@
         <v>40.3</v>
       </c>
       <c r="M87">
-        <v>72.692612</v>
+        <v>73.54781920000001</v>
       </c>
       <c r="N87">
-        <v>-32.392612</v>
+        <v>-33.24781920000001</v>
       </c>
       <c r="O87">
-        <v>-8.098153</v>
+        <v>-8.311954800000002</v>
       </c>
       <c r="P87">
-        <v>-24.294459</v>
+        <v>-24.93586440000001</v>
       </c>
       <c r="Q87">
-        <v>-23.094459</v>
+        <v>-23.73586440000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.344362057107261</v>
+        <v>0.3656879183292082</v>
       </c>
       <c r="T87">
-        <v>5.984276354761026</v>
+        <v>6.411724665815385</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1385973033958389</v>
+        <v>0.1369857068447245</v>
       </c>
       <c r="W87">
-        <v>0.1729696614781156</v>
+        <v>0.1732932700655793</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5543892135833557</v>
+        <v>0.547942827378898</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2002285208224874</v>
+        <v>0.2017785208224874</v>
       </c>
       <c r="C88">
-        <v>-137.0143748638552</v>
+        <v>-142.5740769313283</v>
       </c>
       <c r="D88">
-        <v>162.2596251361448</v>
+        <v>160.9589230686716</v>
       </c>
       <c r="E88">
-        <v>313.274</v>
+        <v>317.533</v>
       </c>
       <c r="F88">
-        <v>366.274</v>
+        <v>370.533</v>
       </c>
       <c r="G88">
         <v>67</v>
@@ -8491,37 +8491,37 @@
         <v>40.3</v>
       </c>
       <c r="M88">
-        <v>73.54781920000001</v>
+        <v>74.40302639999999</v>
       </c>
       <c r="N88">
-        <v>-33.24781920000001</v>
+        <v>-34.10302639999999</v>
       </c>
       <c r="O88">
-        <v>-8.311954800000002</v>
+        <v>-8.525756599999998</v>
       </c>
       <c r="P88">
-        <v>-24.93586440000001</v>
+        <v>-25.57726979999999</v>
       </c>
       <c r="Q88">
-        <v>-23.73586440000001</v>
+        <v>-24.37726979999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3656879183292082</v>
+        <v>0.3902946812776088</v>
       </c>
       <c r="T88">
-        <v>6.411724665815385</v>
+        <v>6.904934255493491</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1369857068447245</v>
+        <v>0.1354111584901874</v>
       </c>
       <c r="W88">
-        <v>0.1732932700655793</v>
+        <v>0.1736094393751704</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.547942827378898</v>
+        <v>0.5416446339607498</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2017785208224874</v>
+        <v>0.2033285208224874</v>
       </c>
       <c r="C89">
-        <v>-142.5740769313283</v>
+        <v>-148.1130915142844</v>
       </c>
       <c r="D89">
-        <v>160.9589230686716</v>
+        <v>159.6789084857156</v>
       </c>
       <c r="E89">
-        <v>317.533</v>
+        <v>321.792</v>
       </c>
       <c r="F89">
-        <v>370.533</v>
+        <v>374.792</v>
       </c>
       <c r="G89">
         <v>67</v>
@@ -8573,37 +8573,37 @@
         <v>40.3</v>
       </c>
       <c r="M89">
-        <v>74.40302639999999</v>
+        <v>75.2582336</v>
       </c>
       <c r="N89">
-        <v>-34.10302639999999</v>
+        <v>-34.9582336</v>
       </c>
       <c r="O89">
-        <v>-8.525756599999998</v>
+        <v>-8.7395584</v>
       </c>
       <c r="P89">
-        <v>-25.57726979999999</v>
+        <v>-26.2186752</v>
       </c>
       <c r="Q89">
-        <v>-24.37726979999999</v>
+        <v>-25.0186752</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3902946812776088</v>
+        <v>0.4190025713840763</v>
       </c>
       <c r="T89">
-        <v>6.904934255493491</v>
+        <v>7.480345443451284</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1354111584901874</v>
+        <v>0.1338723953255262</v>
       </c>
       <c r="W89">
-        <v>0.1736094393751704</v>
+        <v>0.1739184230186343</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5416446339607498</v>
+        <v>0.5354895813021048</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2033285208224874</v>
+        <v>0.2048785208224874</v>
       </c>
       <c r="C90">
-        <v>-148.1130915142844</v>
+        <v>-153.6319082661119</v>
       </c>
       <c r="D90">
-        <v>159.6789084857156</v>
+        <v>158.4190917338881</v>
       </c>
       <c r="E90">
-        <v>321.792</v>
+        <v>326.051</v>
       </c>
       <c r="F90">
-        <v>374.792</v>
+        <v>379.051</v>
       </c>
       <c r="G90">
         <v>67</v>
@@ -8655,37 +8655,37 @@
         <v>40.3</v>
       </c>
       <c r="M90">
-        <v>75.2582336</v>
+        <v>76.11344080000001</v>
       </c>
       <c r="N90">
-        <v>-34.9582336</v>
+        <v>-35.81344080000001</v>
       </c>
       <c r="O90">
-        <v>-8.7395584</v>
+        <v>-8.953360200000002</v>
       </c>
       <c r="P90">
-        <v>-26.2186752</v>
+        <v>-26.86008060000001</v>
       </c>
       <c r="Q90">
-        <v>-25.0186752</v>
+        <v>-25.66008060000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4190025713840763</v>
+        <v>0.4529300778735378</v>
       </c>
       <c r="T90">
-        <v>7.480345443451284</v>
+        <v>8.160376847401402</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1338723953255262</v>
+        <v>0.1323682111083855</v>
       </c>
       <c r="W90">
-        <v>0.1739184230186343</v>
+        <v>0.1742204632094362</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5354895813021048</v>
+        <v>0.5294728444335418</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2048785208224874</v>
+        <v>0.2064285208224874</v>
       </c>
       <c r="C91">
-        <v>-153.6319082661119</v>
+        <v>-159.1310015083137</v>
       </c>
       <c r="D91">
-        <v>158.4190917338881</v>
+        <v>157.1789984916863</v>
       </c>
       <c r="E91">
-        <v>326.051</v>
+        <v>330.31</v>
       </c>
       <c r="F91">
-        <v>379.051</v>
+        <v>383.31</v>
       </c>
       <c r="G91">
         <v>67</v>
@@ -8737,37 +8737,37 @@
         <v>40.3</v>
       </c>
       <c r="M91">
-        <v>76.11344080000001</v>
+        <v>76.968648</v>
       </c>
       <c r="N91">
-        <v>-35.81344080000001</v>
+        <v>-36.668648</v>
       </c>
       <c r="O91">
-        <v>-8.953360200000002</v>
+        <v>-9.167162000000001</v>
       </c>
       <c r="P91">
-        <v>-26.86008060000001</v>
+        <v>-27.501486</v>
       </c>
       <c r="Q91">
-        <v>-25.66008060000001</v>
+        <v>-26.301486</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4529300778735378</v>
+        <v>0.4936430856608916</v>
       </c>
       <c r="T91">
-        <v>8.160376847401402</v>
+        <v>8.976414532141542</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1323682111083855</v>
+        <v>0.1308974532071812</v>
       </c>
       <c r="W91">
-        <v>0.1742204632094362</v>
+        <v>0.174515791395998</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5294728444335418</v>
+        <v>0.5235898128287246</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2064285208224874</v>
+        <v>0.2079785208224874</v>
       </c>
       <c r="C92">
-        <v>-159.1310015083137</v>
+        <v>-164.6108308259303</v>
       </c>
       <c r="D92">
-        <v>157.1789984916863</v>
+        <v>155.9581691740697</v>
       </c>
       <c r="E92">
-        <v>330.31</v>
+        <v>334.569</v>
       </c>
       <c r="F92">
-        <v>383.31</v>
+        <v>387.569</v>
       </c>
       <c r="G92">
         <v>67</v>
@@ -8819,37 +8819,37 @@
         <v>40.3</v>
       </c>
       <c r="M92">
-        <v>76.968648</v>
+        <v>77.82385520000001</v>
       </c>
       <c r="N92">
-        <v>-36.668648</v>
+        <v>-37.52385520000001</v>
       </c>
       <c r="O92">
-        <v>-9.167162000000001</v>
+        <v>-9.380963800000004</v>
       </c>
       <c r="P92">
-        <v>-27.501486</v>
+        <v>-28.14289140000001</v>
       </c>
       <c r="Q92">
-        <v>-26.301486</v>
+        <v>-26.94289140000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4936430856608916</v>
+        <v>0.5434034285121019</v>
       </c>
       <c r="T92">
-        <v>8.976414532141542</v>
+        <v>9.973793924601715</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1308974532071812</v>
+        <v>0.1294590196554539</v>
       </c>
       <c r="W92">
-        <v>0.174515791395998</v>
+        <v>0.1748046288531848</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5235898128287246</v>
+        <v>0.5178360786218156</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2079785208224874</v>
+        <v>0.2095285208224874</v>
       </c>
       <c r="C93">
-        <v>-164.6108308259303</v>
+        <v>-170.071841635429</v>
       </c>
       <c r="D93">
-        <v>155.9581691740697</v>
+        <v>154.756158364571</v>
       </c>
       <c r="E93">
-        <v>334.569</v>
+        <v>338.828</v>
       </c>
       <c r="F93">
-        <v>387.569</v>
+        <v>391.828</v>
       </c>
       <c r="G93">
         <v>67</v>
@@ -8901,37 +8901,37 @@
         <v>40.3</v>
       </c>
       <c r="M93">
-        <v>77.82385520000001</v>
+        <v>78.67906239999999</v>
       </c>
       <c r="N93">
-        <v>-37.52385520000001</v>
+        <v>-38.3790624</v>
       </c>
       <c r="O93">
-        <v>-9.380963800000004</v>
+        <v>-9.594765599999999</v>
       </c>
       <c r="P93">
-        <v>-28.14289140000001</v>
+        <v>-28.7842968</v>
       </c>
       <c r="Q93">
-        <v>-26.94289140000001</v>
+        <v>-27.5842968</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5434034285121019</v>
+        <v>0.6056038570761146</v>
       </c>
       <c r="T93">
-        <v>9.973793924601715</v>
+        <v>11.22051816517693</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1294590196554539</v>
+        <v>0.1280518563983294</v>
       </c>
       <c r="W93">
-        <v>0.1748046288531848</v>
+        <v>0.1750871872352155</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5178360786218156</v>
+        <v>0.5122074255933178</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2095285208224874</v>
+        <v>0.2110785208224874</v>
       </c>
       <c r="C94">
-        <v>-170.071841635429</v>
+        <v>-175.5144657265325</v>
       </c>
       <c r="D94">
-        <v>154.756158364571</v>
+        <v>153.5725342734675</v>
       </c>
       <c r="E94">
-        <v>338.828</v>
+        <v>343.087</v>
       </c>
       <c r="F94">
-        <v>391.828</v>
+        <v>396.087</v>
       </c>
       <c r="G94">
         <v>67</v>
@@ -8983,37 +8983,37 @@
         <v>40.3</v>
       </c>
       <c r="M94">
-        <v>78.67906239999999</v>
+        <v>79.5342696</v>
       </c>
       <c r="N94">
-        <v>-38.3790624</v>
+        <v>-39.2342696</v>
       </c>
       <c r="O94">
-        <v>-9.594765599999999</v>
+        <v>-9.808567400000001</v>
       </c>
       <c r="P94">
-        <v>-28.7842968</v>
+        <v>-29.4257022</v>
       </c>
       <c r="Q94">
-        <v>-27.5842968</v>
+        <v>-28.2257022</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6056038570761146</v>
+        <v>0.6855758366584168</v>
       </c>
       <c r="T94">
-        <v>11.22051816517693</v>
+        <v>12.82344933163078</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1280518563983294</v>
+        <v>0.126674954716627</v>
       </c>
       <c r="W94">
-        <v>0.1750871872352155</v>
+        <v>0.1753636690929013</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5122074255933178</v>
+        <v>0.5066998188665077</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2110785208224874</v>
+        <v>0.2126285208224874</v>
       </c>
       <c r="C95">
-        <v>-175.5144657265325</v>
+        <v>-180.9391217793718</v>
       </c>
       <c r="D95">
-        <v>153.5725342734675</v>
+        <v>152.4068782206282</v>
       </c>
       <c r="E95">
-        <v>343.087</v>
+        <v>347.346</v>
       </c>
       <c r="F95">
-        <v>396.087</v>
+        <v>400.346</v>
       </c>
       <c r="G95">
         <v>67</v>
@@ -9065,37 +9065,37 @@
         <v>40.3</v>
       </c>
       <c r="M95">
-        <v>79.5342696</v>
+        <v>80.3894768</v>
       </c>
       <c r="N95">
-        <v>-39.2342696</v>
+        <v>-40.0894768</v>
       </c>
       <c r="O95">
-        <v>-9.808567400000001</v>
+        <v>-10.0223692</v>
       </c>
       <c r="P95">
-        <v>-29.4257022</v>
+        <v>-30.0671076</v>
       </c>
       <c r="Q95">
-        <v>-28.2257022</v>
+        <v>-28.8671076</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6855758366584168</v>
+        <v>0.7922051427681532</v>
       </c>
       <c r="T95">
-        <v>12.82344933163078</v>
+        <v>14.96069088690258</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.126674954716627</v>
+        <v>0.1253273488153862</v>
       </c>
       <c r="W95">
-        <v>0.1753636690929013</v>
+        <v>0.1756342683578705</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5066998188665077</v>
+        <v>0.5013093952615449</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2126285208224874</v>
+        <v>0.2483162092626463</v>
       </c>
       <c r="C96">
-        <v>-180.9391217793718</v>
+        <v>-207.8705887526987</v>
       </c>
       <c r="D96">
-        <v>152.4068782206282</v>
+        <v>129.7344112473013</v>
       </c>
       <c r="E96">
-        <v>347.346</v>
+        <v>351.605</v>
       </c>
       <c r="F96">
-        <v>400.346</v>
+        <v>404.605</v>
       </c>
       <c r="G96">
         <v>67</v>
@@ -9147,45 +9147,45 @@
         <v>40.3</v>
       </c>
       <c r="M96">
-        <v>80.3894768</v>
+        <v>95.40585900000001</v>
       </c>
       <c r="N96">
-        <v>-40.0894768</v>
+        <v>-55.10585900000001</v>
       </c>
       <c r="O96">
-        <v>-10.0223692</v>
+        <v>-13.77646475</v>
       </c>
       <c r="P96">
-        <v>-30.0671076</v>
+        <v>-41.32939425000001</v>
       </c>
       <c r="Q96">
-        <v>-28.8671076</v>
+        <v>-40.12939425</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7922051427681532</v>
+        <v>0.9592399401249625</v>
       </c>
       <c r="T96">
-        <v>14.96069088690258</v>
+        <v>18.30867956948841</v>
       </c>
       <c r="U96">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1253273488153862</v>
+        <v>0.1056014809321092</v>
       </c>
       <c r="W96">
-        <v>0.1756342683578705</v>
+        <v>0.2108991707962087</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.5013093952615449</v>
+        <v>0.4224059237284368</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2483162092626463</v>
+        <v>0.2502162092626463</v>
       </c>
       <c r="C97">
-        <v>-207.8705887526987</v>
+        <v>-213.1490212690055</v>
       </c>
       <c r="D97">
-        <v>129.7344112473013</v>
+        <v>128.7149787309945</v>
       </c>
       <c r="E97">
-        <v>351.605</v>
+        <v>355.864</v>
       </c>
       <c r="F97">
-        <v>404.605</v>
+        <v>408.864</v>
       </c>
       <c r="G97">
         <v>67</v>
@@ -9229,37 +9229,37 @@
         <v>40.3</v>
       </c>
       <c r="M97">
-        <v>95.40585900000001</v>
+        <v>96.41013120000001</v>
       </c>
       <c r="N97">
-        <v>-55.10585900000001</v>
+        <v>-56.11013120000001</v>
       </c>
       <c r="O97">
-        <v>-13.77646475</v>
+        <v>-14.0275328</v>
       </c>
       <c r="P97">
-        <v>-41.32939425000001</v>
+        <v>-42.08259840000001</v>
       </c>
       <c r="Q97">
-        <v>-40.12939425</v>
+        <v>-40.88259840000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9592399401249625</v>
+        <v>1.187599925156204</v>
       </c>
       <c r="T97">
-        <v>18.30867956948841</v>
+        <v>22.88584946186052</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1056014809321092</v>
+        <v>0.1045014655057331</v>
       </c>
       <c r="W97">
-        <v>0.2108991707962087</v>
+        <v>0.2111585544337482</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4224059237284368</v>
+        <v>0.4180058620229322</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2502162092626463</v>
+        <v>0.2521162092626463</v>
       </c>
       <c r="C98">
-        <v>-213.1490212690055</v>
+        <v>-218.41155761545</v>
       </c>
       <c r="D98">
-        <v>128.7149787309945</v>
+        <v>127.71144238455</v>
       </c>
       <c r="E98">
-        <v>355.864</v>
+        <v>360.123</v>
       </c>
       <c r="F98">
-        <v>408.864</v>
+        <v>413.123</v>
       </c>
       <c r="G98">
         <v>67</v>
@@ -9311,37 +9311,37 @@
         <v>40.3</v>
       </c>
       <c r="M98">
-        <v>96.4101312</v>
+        <v>97.4144034</v>
       </c>
       <c r="N98">
-        <v>-56.1101312</v>
+        <v>-57.1144034</v>
       </c>
       <c r="O98">
-        <v>-14.0275328</v>
+        <v>-14.27860085</v>
       </c>
       <c r="P98">
-        <v>-42.08259839999999</v>
+        <v>-42.83580255</v>
       </c>
       <c r="Q98">
-        <v>-40.88259839999999</v>
+        <v>-41.63580254999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.187599925156201</v>
+        <v>1.568199900208268</v>
       </c>
       <c r="T98">
-        <v>22.88584946186046</v>
+        <v>30.51446594914728</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1045014655057331</v>
+        <v>0.1034241308097977</v>
       </c>
       <c r="W98">
-        <v>0.2111585544337482</v>
+        <v>0.2114125899550497</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4180058620229323</v>
+        <v>0.4136965232391907</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2521162092626463</v>
+        <v>0.2540162092626463</v>
       </c>
       <c r="C99">
-        <v>-218.41155761545</v>
+        <v>-223.6585667228102</v>
       </c>
       <c r="D99">
-        <v>127.71144238455</v>
+        <v>126.7234332771898</v>
       </c>
       <c r="E99">
-        <v>360.123</v>
+        <v>364.3819999999999</v>
       </c>
       <c r="F99">
-        <v>413.123</v>
+        <v>417.3819999999999</v>
       </c>
       <c r="G99">
         <v>67</v>
@@ -9393,37 +9393,37 @@
         <v>40.3</v>
       </c>
       <c r="M99">
-        <v>97.4144034</v>
+        <v>98.41867559999999</v>
       </c>
       <c r="N99">
-        <v>-57.1144034</v>
+        <v>-58.11867559999999</v>
       </c>
       <c r="O99">
-        <v>-14.27860085</v>
+        <v>-14.5296689</v>
       </c>
       <c r="P99">
-        <v>-42.83580255</v>
+        <v>-43.58900669999999</v>
       </c>
       <c r="Q99">
-        <v>-41.63580254999999</v>
+        <v>-42.38900669999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.568199900208268</v>
+        <v>2.329399850312401</v>
       </c>
       <c r="T99">
-        <v>30.51446594914728</v>
+        <v>45.77169892372092</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1034241308097977</v>
+        <v>0.1023687825362283</v>
       </c>
       <c r="W99">
-        <v>0.2114125899550497</v>
+        <v>0.2116614410779574</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4136965232391907</v>
+        <v>0.4094751301449133</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2540162092626463</v>
+        <v>0.2559162092626462</v>
       </c>
       <c r="C100">
-        <v>-223.6585667228102</v>
+        <v>-228.8904061929278</v>
       </c>
       <c r="D100">
-        <v>126.7234332771898</v>
+        <v>125.7505938070722</v>
       </c>
       <c r="E100">
-        <v>364.3819999999999</v>
+        <v>368.641</v>
       </c>
       <c r="F100">
-        <v>417.3819999999999</v>
+        <v>421.641</v>
       </c>
       <c r="G100">
         <v>67</v>
@@ -9475,37 +9475,37 @@
         <v>40.3</v>
       </c>
       <c r="M100">
-        <v>98.41867559999999</v>
+        <v>99.42294779999999</v>
       </c>
       <c r="N100">
-        <v>-58.11867559999999</v>
+        <v>-59.12294779999999</v>
       </c>
       <c r="O100">
-        <v>-14.5296689</v>
+        <v>-14.78073695</v>
       </c>
       <c r="P100">
-        <v>-43.58900669999999</v>
+        <v>-44.34221084999999</v>
       </c>
       <c r="Q100">
-        <v>-42.38900669999999</v>
+        <v>-43.14221084999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.329399850312401</v>
+        <v>4.612999700624801</v>
       </c>
       <c r="T100">
-        <v>45.77169892372092</v>
+        <v>91.54339784744182</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1023687825362283</v>
+        <v>0.1013347544298018</v>
       </c>
       <c r="W100">
-        <v>0.2116614410779574</v>
+        <v>0.2119052649054528</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4094751301449133</v>
+        <v>0.4053390177192071</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2559162092626462</v>
-      </c>
-      <c r="C101">
-        <v>-228.8904061929278</v>
-      </c>
-      <c r="D101">
-        <v>125.7505938070722</v>
-      </c>
-      <c r="E101">
-        <v>368.641</v>
-      </c>
-      <c r="F101">
-        <v>421.641</v>
-      </c>
-      <c r="G101">
-        <v>67</v>
-      </c>
-      <c r="H101">
-        <v>372.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>41.5</v>
-      </c>
-      <c r="K101">
-        <v>1.2</v>
-      </c>
-      <c r="L101">
-        <v>40.3</v>
-      </c>
-      <c r="M101">
-        <v>99.42294779999999</v>
-      </c>
-      <c r="N101">
-        <v>-59.12294779999999</v>
-      </c>
-      <c r="O101">
-        <v>-14.78073695</v>
-      </c>
-      <c r="P101">
-        <v>-44.34221084999999</v>
-      </c>
-      <c r="Q101">
-        <v>-43.14221084999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.612999700624801</v>
-      </c>
-      <c r="T101">
-        <v>91.54339784744182</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1013347544298018</v>
-      </c>
-      <c r="W101">
-        <v>0.2119052649054528</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4053390177192071</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
